--- a/resources/commonlab.xlsx
+++ b/resources/commonlab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owais\workspace\openmrs-tajikistan\openmrs-mdrtb-etl-job\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697A2F33-10E6-4D70-B83B-5243782A6A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A70076A-3942-4F27-9749-647B2DAC8DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="640" activeTab="1" xr2:uid="{18076D00-A540-4435-B04D-A40348706011}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="640" xr2:uid="{18076D00-A540-4435-B04D-A40348706011}"/>
   </bookViews>
   <sheets>
     <sheet name="test_types" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="413">
   <si>
     <t>uuid</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>HAIN 2 TEST</t>
-  </si>
-  <si>
-    <t>MICROBIOLOGY</t>
   </si>
   <si>
     <t>short_name</t>
@@ -1749,16 +1746,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>0</v>
@@ -1769,16 +1766,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1787,7 +1784,7 @@
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1798,10 +1795,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
@@ -1813,7 +1810,7 @@
         <v>311</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1824,10 +1821,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -1839,7 +1836,7 @@
         <v>323</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1850,10 +1847,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -1865,7 +1862,7 @@
         <v>153</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1873,16 +1870,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1891,7 +1888,7 @@
         <v>410</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1902,13 +1899,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1917,7 +1914,7 @@
         <v>414</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1925,16 +1922,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1943,7 +1940,7 @@
         <v>572</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1951,16 +1948,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1969,7 +1966,7 @@
         <v>573</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2005,52 +2002,52 @@
   <sheetData>
     <row r="1" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>0</v>
@@ -2064,19 +2061,19 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>40</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -2086,7 +2083,7 @@
         <v xml:space="preserve">DATE COLLECTED </v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
@@ -2101,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2112,10 +2109,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2132,7 +2129,7 @@
         <v xml:space="preserve">INVESTIGATION DATE </v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K3"/>
       <c r="L3"/>
@@ -2147,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2158,11 +2155,11 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
         <v>48</v>
       </c>
-      <c r="D4" t="s">
-        <v>49</v>
-      </c>
       <c r="E4">
         <v>0</v>
       </c>
@@ -2170,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -2180,7 +2177,7 @@
         <v xml:space="preserve">LABORATORY INVESTIGATION NUMBER </v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K4"/>
       <c r="L4"/>
@@ -2195,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2206,19 +2203,19 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>55</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -2228,7 +2225,7 @@
         <v xml:space="preserve">PURPOSE OF INVESTIGATION </v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K5"/>
       <c r="L5"/>
@@ -2243,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2254,10 +2251,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
         <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>58</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2274,7 +2271,7 @@
         <v xml:space="preserve">REFERRING FACILITY </v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
@@ -2289,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2300,19 +2297,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
         <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -2322,7 +2319,7 @@
         <v xml:space="preserve">REQUESTING MEDICAL FACILITY </v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K7"/>
       <c r="L7"/>
@@ -2337,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2348,10 +2345,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2360,7 +2357,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -2370,7 +2367,7 @@
         <v xml:space="preserve">TUBERCULOSIS SAMPLE SOURCE </v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8"/>
       <c r="L8"/>
@@ -2385,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2396,10 +2393,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
         <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2416,7 +2413,7 @@
         <v xml:space="preserve">DATE OF REQUEST FOR LABORATORY INVESTIGATION </v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9"/>
       <c r="L9"/>
@@ -2431,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2442,19 +2439,19 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
         <v>45</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>46</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -2464,7 +2461,7 @@
         <v xml:space="preserve">LAB SPECIALIST NAME </v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10"/>
       <c r="L10"/>
@@ -2479,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2490,19 +2487,19 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
         <v>65</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>66</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -2512,7 +2509,7 @@
         <v xml:space="preserve">TUBERCULOSIS SPECIMEN COMMENTS </v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K11"/>
       <c r="L11"/>
@@ -2527,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2538,19 +2535,19 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>45</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>46</v>
       </c>
       <c r="H12">
         <v>11</v>
@@ -2560,7 +2557,7 @@
         <v xml:space="preserve">REFERRED BY </v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K12"/>
       <c r="L12"/>
@@ -2575,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2586,19 +2583,19 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
         <v>49</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -2608,7 +2605,7 @@
         <v xml:space="preserve">WEIGHT </v>
       </c>
       <c r="J13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13"/>
       <c r="L13"/>
@@ -2623,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2634,10 +2631,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2646,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -2656,7 +2653,7 @@
         <v xml:space="preserve">TUBERCULOSIS SPECIMEN ID </v>
       </c>
       <c r="J14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K14"/>
       <c r="L14"/>
@@ -2671,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2682,19 +2679,19 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
         <v>49</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>50</v>
       </c>
       <c r="H15">
         <v>14</v>
@@ -2704,7 +2701,7 @@
         <v xml:space="preserve">MONTH OF TREATMENT </v>
       </c>
       <c r="J15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K15"/>
       <c r="L15"/>
@@ -2719,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2730,19 +2727,19 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>50</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -2752,7 +2749,7 @@
         <v xml:space="preserve">PATIENT PROGRAM ID </v>
       </c>
       <c r="J16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K16"/>
       <c r="L16"/>
@@ -2767,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2778,10 +2775,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2790,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -2800,7 +2797,7 @@
         <v xml:space="preserve">ISONIAZID RESISTANCE </v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K17"/>
       <c r="L17"/>
@@ -2815,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2826,10 +2823,10 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2838,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -2848,7 +2845,7 @@
         <v xml:space="preserve">RIFAMPICIN RESISTANCE </v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K18"/>
       <c r="L18"/>
@@ -2863,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2874,19 +2871,19 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
+        <v>400</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
         <v>401</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>402</v>
       </c>
       <c r="H19">
         <v>18</v>
@@ -2896,7 +2893,7 @@
         <v xml:space="preserve">INJECTABLE RESISTANCE </v>
       </c>
       <c r="J19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K19"/>
       <c r="L19"/>
@@ -2911,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2922,19 +2919,19 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
         <v>36</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>37</v>
       </c>
       <c r="H20">
         <v>19</v>
@@ -2944,7 +2941,7 @@
         <v>APPEARANCE OF SPECIMEN XPERT</v>
       </c>
       <c r="J20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K20"/>
       <c r="L20" t="s">
@@ -2961,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2972,19 +2969,19 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
         <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>53</v>
       </c>
       <c r="H21">
         <v>20</v>
@@ -2994,7 +2991,7 @@
         <v>MTB RESULT XPERT</v>
       </c>
       <c r="J21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K21"/>
       <c r="L21" t="s">
@@ -3011,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3022,19 +3019,19 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
         <v>45</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>46</v>
       </c>
       <c r="H22">
         <v>21</v>
@@ -3044,7 +3041,7 @@
         <v>ERROR CODE XPERT</v>
       </c>
       <c r="J22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22"/>
       <c r="L22" t="s">
@@ -3061,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3072,19 +3069,19 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
         <v>87</v>
-      </c>
-      <c r="D23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>88</v>
       </c>
       <c r="H23">
         <v>22</v>
@@ -3094,7 +3091,7 @@
         <v>XPERT MTB BURDEN XPERT</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K23"/>
       <c r="L23" t="s">
@@ -3111,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -3122,10 +3119,10 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -3134,7 +3131,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24">
         <v>23</v>
@@ -3144,7 +3141,7 @@
         <v>ISONIAZID RESULT XPERT</v>
       </c>
       <c r="J24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>4</v>
@@ -3159,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3170,10 +3167,10 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -3182,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H25">
         <v>24</v>
@@ -3192,7 +3189,7 @@
         <v>RIFAMPICIN RESULT XPERT</v>
       </c>
       <c r="J25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>4</v>
@@ -3207,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3218,10 +3215,10 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -3238,7 +3235,7 @@
         <v>TUBERCULOSIS TEST RESULT DATE XPERT</v>
       </c>
       <c r="J26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
@@ -3255,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3266,10 +3263,10 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3286,7 +3283,7 @@
         <v>DATE OF SENDING TO CULTURE XPERT</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K27"/>
       <c r="L27" t="s">
@@ -3303,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3314,10 +3311,10 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -3334,7 +3331,7 @@
         <v>DATE OF SENDING TO DST XPERT</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K28"/>
       <c r="L28" t="s">
@@ -3351,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3362,10 +3359,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -3374,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H29">
         <v>28</v>
@@ -3384,7 +3381,7 @@
         <v>SENT TO CULTURE XPERT</v>
       </c>
       <c r="J29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K29"/>
       <c r="L29" t="s">
@@ -3401,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3412,10 +3409,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -3424,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H30">
         <v>29</v>
@@ -3434,7 +3431,7 @@
         <v>SENT TO DST XPERT</v>
       </c>
       <c r="J30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K30"/>
       <c r="L30" t="s">
@@ -3451,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3462,19 +3459,19 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
         <v>36</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>37</v>
       </c>
       <c r="H31">
         <v>30</v>
@@ -3484,7 +3481,7 @@
         <v>APPEARANCE OF SPECIMEN HAIN</v>
       </c>
       <c r="J31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K31"/>
       <c r="L31" t="s">
@@ -3501,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3512,19 +3509,19 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
         <v>52</v>
-      </c>
-      <c r="D32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>53</v>
       </c>
       <c r="H32">
         <v>31</v>
@@ -3534,7 +3531,7 @@
         <v>MTB RESULT HAIN</v>
       </c>
       <c r="J32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K32"/>
       <c r="L32" t="s">
@@ -3551,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3562,19 +3559,19 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
         <v>87</v>
-      </c>
-      <c r="D33" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
       <c r="H33">
         <v>32</v>
@@ -3584,7 +3581,7 @@
         <v>XPERT MTB BURDEN HAIN</v>
       </c>
       <c r="J33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K33"/>
       <c r="L33" t="s">
@@ -3601,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3612,10 +3609,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3624,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H34">
         <v>33</v>
@@ -3634,7 +3631,7 @@
         <v>ISONIAZID RESULT HAIN</v>
       </c>
       <c r="J34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K34"/>
       <c r="L34" t="s">
@@ -3651,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3662,10 +3659,10 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3674,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H35">
         <v>34</v>
@@ -3684,7 +3681,7 @@
         <v>RIFAMPICIN RESULT HAIN</v>
       </c>
       <c r="J35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K35"/>
       <c r="L35" s="1" t="s">
@@ -3701,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -3712,10 +3709,10 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3724,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H36">
         <v>35</v>
@@ -3734,7 +3731,7 @@
         <v>ISONIAZID RESISTANCE HAIN</v>
       </c>
       <c r="J36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>3</v>
@@ -3749,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3760,10 +3757,10 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3772,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H37">
         <v>36</v>
@@ -3782,7 +3779,7 @@
         <v>RIFAMPICIN RESISTANCE HAIN</v>
       </c>
       <c r="J37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L37" t="s">
         <v>3</v>
@@ -3797,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -3808,10 +3805,10 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3820,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H38">
         <v>37</v>
@@ -3830,7 +3827,7 @@
         <v>SENT TO CULTURE HAIN</v>
       </c>
       <c r="J38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L38" t="s">
         <v>3</v>
@@ -3845,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -3856,10 +3853,10 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3868,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H39">
         <v>38</v>
@@ -3878,7 +3875,7 @@
         <v>SENT TO DST HAIN</v>
       </c>
       <c r="J39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L39" t="s">
         <v>3</v>
@@ -3893,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -3904,10 +3901,10 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3923,7 +3920,7 @@
         <v>TUBERCULOSIS TEST RESULT DATE HAIN</v>
       </c>
       <c r="J40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L40" t="s">
         <v>3</v>
@@ -3938,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -3949,10 +3946,10 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3968,7 +3965,7 @@
         <v>DATE OF SENDING TO CULTURE HAIN</v>
       </c>
       <c r="J41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L41" t="s">
         <v>3</v>
@@ -3983,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3994,10 +3991,10 @@
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -4013,7 +4010,7 @@
         <v>DATE OF SENDING TO DST HAIN</v>
       </c>
       <c r="J42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L42" t="s">
         <v>3</v>
@@ -4028,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -4039,19 +4036,19 @@
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
         <v>45</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>46</v>
       </c>
       <c r="H43">
         <v>42</v>
@@ -4061,7 +4058,7 @@
         <v>ERROR CODE HAIN</v>
       </c>
       <c r="J43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L43" t="s">
         <v>3</v>
@@ -4076,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -4087,19 +4084,19 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
         <v>36</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>37</v>
       </c>
       <c r="H44">
         <v>43</v>
@@ -4109,10 +4106,10 @@
         <v>APPEARANCE OF SPECIMEN HAIN2</v>
       </c>
       <c r="J44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -4124,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -4135,19 +4132,19 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
         <v>52</v>
-      </c>
-      <c r="D45" t="s">
-        <v>36</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>53</v>
       </c>
       <c r="H45">
         <v>44</v>
@@ -4157,10 +4154,10 @@
         <v>MTB RESULT HAIN2</v>
       </c>
       <c r="J45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -4172,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -4183,19 +4180,19 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
         <v>87</v>
-      </c>
-      <c r="D46" t="s">
-        <v>36</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>88</v>
       </c>
       <c r="H46">
         <v>45</v>
@@ -4205,10 +4202,10 @@
         <v>XPERT MTB BURDEN HAIN2</v>
       </c>
       <c r="J46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -4220,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -4231,10 +4228,10 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -4243,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H47">
         <v>46</v>
@@ -4253,10 +4250,10 @@
         <v>ISONIAZID RESULT HAIN2</v>
       </c>
       <c r="J47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -4268,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -4279,10 +4276,10 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -4291,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H48">
         <v>47</v>
@@ -4301,10 +4298,10 @@
         <v>RIFAMPICIN RESULT HAIN2</v>
       </c>
       <c r="J48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -4316,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -4327,10 +4324,10 @@
         <v>5</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -4339,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H49">
         <v>48</v>
@@ -4349,10 +4346,10 @@
         <v>ETHAMBUTOL RESULT HAIN2</v>
       </c>
       <c r="J49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -4364,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -4375,10 +4372,10 @@
         <v>5</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4387,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H50">
         <v>49</v>
@@ -4397,10 +4394,10 @@
         <v>КМ/АМ/СМ RESULT HAIN2</v>
       </c>
       <c r="J50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N50">
         <v>1</v>
@@ -4412,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -4423,10 +4420,10 @@
         <v>5</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4435,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H51">
         <v>50</v>
@@ -4445,10 +4442,10 @@
         <v>MOX/OFX RESULT HAIN2</v>
       </c>
       <c r="J51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -4460,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -4471,10 +4468,10 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -4483,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H52">
         <v>51</v>
@@ -4493,10 +4490,10 @@
         <v>SENT TO CULTURE HAIN2</v>
       </c>
       <c r="J52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -4508,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -4519,10 +4516,10 @@
         <v>5</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -4538,10 +4535,10 @@
         <v>TUBERCULOSIS TEST RESULT DATE HAIN2</v>
       </c>
       <c r="J53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -4553,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -4564,10 +4561,10 @@
         <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -4583,10 +4580,10 @@
         <v>DATE OF SENDING TO CULTURE HAIN2</v>
       </c>
       <c r="J54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -4598,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -4609,10 +4606,10 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -4628,10 +4625,10 @@
         <v>DATE OF SENDING TO DST HAIN2</v>
       </c>
       <c r="J55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -4643,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -4654,19 +4651,19 @@
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D56" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
         <v>45</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>46</v>
       </c>
       <c r="H56">
         <v>55</v>
@@ -4676,10 +4673,10 @@
         <v>ERROR CODE HAIN2</v>
       </c>
       <c r="J56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -4691,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -4702,10 +4699,10 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4714,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H57">
         <v>56</v>
@@ -4724,7 +4721,7 @@
         <v>TUBERCULOSIS CULTURE METHOD CULTURE</v>
       </c>
       <c r="J57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>6</v>
@@ -4739,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -4750,10 +4747,10 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4762,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H58">
         <v>57</v>
@@ -4772,7 +4769,7 @@
         <v>TYPE OF ORGANISM CULTURE</v>
       </c>
       <c r="J58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>6</v>
@@ -4787,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -4798,19 +4795,19 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
         <v>45</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>46</v>
       </c>
       <c r="H59">
         <v>58</v>
@@ -4820,7 +4817,7 @@
         <v>TYPE OF ORGANISM NON-CODED CULTURE</v>
       </c>
       <c r="J59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>6</v>
@@ -4835,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="Q59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -4846,10 +4843,10 @@
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4858,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H60">
         <v>59</v>
@@ -4868,7 +4865,7 @@
         <v>MGIT CULTURE RESULT CULTURE</v>
       </c>
       <c r="J60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>6</v>
@@ -4883,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -4894,10 +4891,10 @@
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4906,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H61">
         <v>60</v>
@@ -4916,7 +4913,7 @@
         <v>MT ID TEST CULTURE</v>
       </c>
       <c r="J61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>6</v>
@@ -4931,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -4942,10 +4939,10 @@
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4954,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H62">
         <v>61</v>
@@ -4964,7 +4961,7 @@
         <v>PLACE OF CULTURE CULTURE</v>
       </c>
       <c r="J62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>6</v>
@@ -4979,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="Q62" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -4990,10 +4987,10 @@
         <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -5002,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H63">
         <v>62</v>
@@ -5012,7 +5009,7 @@
         <v>TUBERCULOSIS CULTURE RESULT CULTURE</v>
       </c>
       <c r="J63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>6</v>
@@ -5027,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -5038,10 +5035,10 @@
         <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -5050,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H64">
         <v>63</v>
@@ -5060,7 +5057,7 @@
         <v>TYPE OF CULTURE REPORTED CULTURE</v>
       </c>
       <c r="J64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>6</v>
@@ -5075,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -5086,10 +5083,10 @@
         <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -5105,7 +5102,7 @@
         <v>DATE OF INOCULATION OF CULTURE CULTURE</v>
       </c>
       <c r="J65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>6</v>
@@ -5120,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="Q65" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -5131,10 +5128,10 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -5150,7 +5147,7 @@
         <v>DATE OF REPORTING CULTURE RESULT CULTURE</v>
       </c>
       <c r="J66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>6</v>
@@ -5165,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -5176,10 +5173,10 @@
         <v>5</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5195,7 +5192,7 @@
         <v>TUBERCULOSIS TEST RESULT DATE CULTURE</v>
       </c>
       <c r="J67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>6</v>
@@ -5210,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="Q67" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -5221,19 +5218,19 @@
         <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D68" t="s">
+        <v>48</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
         <v>49</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>50</v>
       </c>
       <c r="H68">
         <v>67</v>
@@ -5243,7 +5240,7 @@
         <v>LABORATORY NO CULTURE</v>
       </c>
       <c r="J68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>6</v>
@@ -5258,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="Q68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -5269,19 +5266,19 @@
         <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D69" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
         <v>49</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69" t="s">
-        <v>50</v>
       </c>
       <c r="H69">
         <v>68</v>
@@ -5291,7 +5288,7 @@
         <v>COLONIES CULTURE</v>
       </c>
       <c r="J69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>6</v>
@@ -5306,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -5317,19 +5314,19 @@
         <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D70" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
         <v>49</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-      <c r="G70" t="s">
-        <v>50</v>
       </c>
       <c r="H70">
         <v>69</v>
@@ -5339,7 +5336,7 @@
         <v>DAYS TO POSITIVITY CULTURE</v>
       </c>
       <c r="J70" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>6</v>
@@ -5354,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="Q70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -5365,19 +5362,19 @@
         <v>5</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
         <v>36</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71" t="s">
-        <v>37</v>
       </c>
       <c r="H71">
         <v>70</v>
@@ -5387,7 +5384,7 @@
         <v>APPEARANCE OF SPECIMEN SMEAR</v>
       </c>
       <c r="J71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>5</v>
@@ -5402,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="Q71" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -5413,19 +5410,19 @@
         <v>5</v>
       </c>
       <c r="C72" t="s">
+        <v>283</v>
+      </c>
+      <c r="D72" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
         <v>284</v>
-      </c>
-      <c r="D72" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72" t="s">
-        <v>285</v>
       </c>
       <c r="H72">
         <v>71</v>
@@ -5435,7 +5432,7 @@
         <v>TUBERCULOSIS SMEAR RESULT SMEAR</v>
       </c>
       <c r="J72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>5</v>
@@ -5450,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="Q72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -5461,10 +5458,10 @@
         <v>5</v>
       </c>
       <c r="C73" t="s">
+        <v>96</v>
+      </c>
+      <c r="D73" t="s">
         <v>97</v>
-      </c>
-      <c r="D73" t="s">
-        <v>98</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5480,7 +5477,7 @@
         <v>BACILLI SMEAR</v>
       </c>
       <c r="J73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>5</v>
@@ -5495,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="Q73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -5506,10 +5503,10 @@
         <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5525,7 +5522,7 @@
         <v>TUBERCULOSIS TEST RESULT DATE SMEAR</v>
       </c>
       <c r="J74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>5</v>
@@ -5540,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="Q74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -5551,10 +5548,10 @@
         <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5563,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H75">
         <v>74</v>
@@ -5573,7 +5570,7 @@
         <v>MICROSCOPY RESULT SMEAR</v>
       </c>
       <c r="J75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>5</v>
@@ -5588,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -5599,10 +5596,10 @@
         <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5618,7 +5615,7 @@
         <v xml:space="preserve">START DATE </v>
       </c>
       <c r="J76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L76" s="1"/>
       <c r="N76">
@@ -5631,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -5642,10 +5639,10 @@
         <v>5</v>
       </c>
       <c r="C77" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5661,7 +5658,7 @@
         <v xml:space="preserve">TUBERCULOSIS TEST DATE RECEIVED </v>
       </c>
       <c r="J77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L77" s="1"/>
       <c r="N77">
@@ -5674,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -5685,10 +5682,10 @@
         <v>5</v>
       </c>
       <c r="C78" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5704,7 +5701,7 @@
         <v xml:space="preserve">TUBERCULOSIS TEST DATE ORDERED </v>
       </c>
       <c r="J78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L78" s="1"/>
       <c r="N78">
@@ -5717,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -5728,10 +5725,10 @@
         <v>5</v>
       </c>
       <c r="C79" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5740,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H79">
         <v>78</v>
@@ -5750,7 +5747,7 @@
         <v xml:space="preserve">SUSCEPTIBLE TO TUBERCULOSIS DRUG </v>
       </c>
       <c r="J79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L79" s="1"/>
       <c r="N79">
@@ -5763,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -5774,10 +5771,10 @@
         <v>5</v>
       </c>
       <c r="C80" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80" t="s">
         <v>99</v>
-      </c>
-      <c r="D80" t="s">
-        <v>100</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5793,7 +5790,7 @@
         <v xml:space="preserve">DIRECT/INDIRECT </v>
       </c>
       <c r="J80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L80" s="1"/>
       <c r="N80">
@@ -5806,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="Q80" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -5817,19 +5814,19 @@
         <v>5</v>
       </c>
       <c r="C81" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D81" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="D81" t="s">
-        <v>36</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="H81">
         <v>80</v>
@@ -5839,10 +5836,10 @@
         <v>TUBERCULOSIS DRUG SENSITIVITY TEST METHOD DST</v>
       </c>
       <c r="J81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -5854,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -5865,10 +5862,10 @@
         <v>5</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5877,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H82">
         <v>81</v>
@@ -5887,10 +5884,10 @@
         <v>AMIKACIN RESISTANCE DST</v>
       </c>
       <c r="J82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5902,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -5913,10 +5910,10 @@
         <v>5</v>
       </c>
       <c r="C83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5925,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H83">
         <v>82</v>
@@ -5935,10 +5932,10 @@
         <v>BEDAQUILINE RESISTANCE DST</v>
       </c>
       <c r="J83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -5950,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="Q83" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -5961,10 +5958,10 @@
         <v>5</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D84" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5973,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H84">
         <v>83</v>
@@ -5983,10 +5980,10 @@
         <v>CAPREOMYCIN RESISTANCE DST</v>
       </c>
       <c r="J84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -5998,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="Q84" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -6009,19 +6006,19 @@
         <v>5</v>
       </c>
       <c r="C85" t="s">
+        <v>130</v>
+      </c>
+      <c r="D85" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
         <v>131</v>
-      </c>
-      <c r="D85" t="s">
-        <v>36</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-      <c r="G85" t="s">
-        <v>132</v>
       </c>
       <c r="H85">
         <v>84</v>
@@ -6031,10 +6028,10 @@
         <v>CIPROFLOXACIN RESISTANCE DST</v>
       </c>
       <c r="J85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -6046,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="Q85" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -6057,19 +6054,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
+        <v>132</v>
+      </c>
+      <c r="D86" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="s">
         <v>133</v>
-      </c>
-      <c r="D86" t="s">
-        <v>36</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="G86" t="s">
-        <v>134</v>
       </c>
       <c r="H86">
         <v>85</v>
@@ -6079,10 +6076,10 @@
         <v>CLARITHROMYCIN RESISTANCE DST</v>
       </c>
       <c r="J86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -6094,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="Q86" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -6105,10 +6102,10 @@
         <v>5</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6117,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H87">
         <v>86</v>
@@ -6127,10 +6124,10 @@
         <v>CLOFAZAMINE RESISTANCE DST</v>
       </c>
       <c r="J87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -6142,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="Q87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -6153,19 +6150,19 @@
         <v>5</v>
       </c>
       <c r="C88" t="s">
+        <v>134</v>
+      </c>
+      <c r="D88" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
         <v>135</v>
-      </c>
-      <c r="D88" t="s">
-        <v>36</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88" t="s">
-        <v>136</v>
       </c>
       <c r="H88">
         <v>87</v>
@@ -6175,10 +6172,10 @@
         <v>CYCLOSERINE RESISTANCE DST</v>
       </c>
       <c r="J88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -6190,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="Q88" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -6201,10 +6198,10 @@
         <v>5</v>
       </c>
       <c r="C89" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -6213,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H89">
         <v>88</v>
@@ -6223,10 +6220,10 @@
         <v>DELAMANID RESISTANCE DST</v>
       </c>
       <c r="J89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -6238,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="Q89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -6249,19 +6246,19 @@
         <v>5</v>
       </c>
       <c r="C90" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
         <v>137</v>
-      </c>
-      <c r="D90" t="s">
-        <v>36</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-      <c r="G90" t="s">
-        <v>138</v>
       </c>
       <c r="H90">
         <v>89</v>
@@ -6271,10 +6268,10 @@
         <v>ETHAMBUTOL RESISTANCE DST</v>
       </c>
       <c r="J90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -6286,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="Q90" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -6297,10 +6294,10 @@
         <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -6309,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H91">
         <v>90</v>
@@ -6319,10 +6316,10 @@
         <v>ETHIONAMIDE RESISTANCE DST</v>
       </c>
       <c r="J91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -6334,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -6345,10 +6342,10 @@
         <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6357,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H92">
         <v>91</v>
@@ -6367,10 +6364,10 @@
         <v>GATIFLOXACIN RESISTANCE DST</v>
       </c>
       <c r="J92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -6382,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -6393,10 +6390,10 @@
         <v>5</v>
       </c>
       <c r="C93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6405,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H93">
         <v>92</v>
@@ -6415,10 +6412,10 @@
         <v>ISONIAZID RESISTANCE DST</v>
       </c>
       <c r="J93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -6430,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -6441,10 +6438,10 @@
         <v>5</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -6453,7 +6450,7 @@
         <v>1</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H94">
         <v>93</v>
@@ -6463,10 +6460,10 @@
         <v>KANAMYCIN RESISTANCE DST</v>
       </c>
       <c r="J94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -6478,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="Q94" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -6489,10 +6486,10 @@
         <v>5</v>
       </c>
       <c r="C95" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6501,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H95">
         <v>94</v>
@@ -6511,10 +6508,10 @@
         <v>LEVOFLOXACIN RESISTANCE DST</v>
       </c>
       <c r="J95" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -6526,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="Q95" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -6537,10 +6534,10 @@
         <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D96" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6549,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H96">
         <v>95</v>
@@ -6559,10 +6556,10 @@
         <v>LINEZOLID RESISTANCE DST</v>
       </c>
       <c r="J96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -6574,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="Q96" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -6585,10 +6582,10 @@
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6597,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H97">
         <v>96</v>
@@ -6607,10 +6604,10 @@
         <v>MOXIFLOXACIN RESISTANCE DST</v>
       </c>
       <c r="J97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N97">
         <v>1</v>
@@ -6622,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="Q97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -6633,10 +6630,10 @@
         <v>5</v>
       </c>
       <c r="C98" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6645,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H98">
         <v>97</v>
@@ -6655,10 +6652,10 @@
         <v>OFLOXACIN RESISTANCE DST</v>
       </c>
       <c r="J98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -6670,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -6681,10 +6678,10 @@
         <v>5</v>
       </c>
       <c r="C99" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6693,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H99">
         <v>98</v>
@@ -6703,10 +6700,10 @@
         <v>OTHER RESISTANCE DST</v>
       </c>
       <c r="J99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -6718,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="Q99" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -6729,10 +6726,10 @@
         <v>5</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6741,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H100">
         <v>99</v>
@@ -6751,10 +6748,10 @@
         <v>P-AMINOSALICY RESISTANCE DST</v>
       </c>
       <c r="J100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -6766,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="Q100" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -6777,10 +6774,10 @@
         <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6789,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H101">
         <v>100</v>
@@ -6799,10 +6796,10 @@
         <v>PROTHIONAMIDE RESISTANCE DST</v>
       </c>
       <c r="J101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N101">
         <v>1</v>
@@ -6814,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -6825,10 +6822,10 @@
         <v>5</v>
       </c>
       <c r="C102" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6837,7 +6834,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H102">
         <v>101</v>
@@ -6847,10 +6844,10 @@
         <v>PYRAZINAMIDE RESISTANCE DST</v>
       </c>
       <c r="J102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N102">
         <v>1</v>
@@ -6862,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="Q102" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -6873,10 +6870,10 @@
         <v>5</v>
       </c>
       <c r="C103" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D103" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6885,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H103">
         <v>102</v>
@@ -6895,10 +6892,10 @@
         <v>PYRIDOXINE RESISTANCE DST</v>
       </c>
       <c r="J103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N103">
         <v>1</v>
@@ -6910,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="Q103" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -6921,10 +6918,10 @@
         <v>5</v>
       </c>
       <c r="C104" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6933,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H104">
         <v>103</v>
@@ -6943,10 +6940,10 @@
         <v>RIFABUTIN RESISTANCE DST</v>
       </c>
       <c r="J104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -6958,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="Q104" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -6969,10 +6966,10 @@
         <v>5</v>
       </c>
       <c r="C105" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6981,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H105">
         <v>104</v>
@@ -6991,10 +6988,10 @@
         <v>RIFAMPICIN RESISTANCE DST</v>
       </c>
       <c r="J105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -7006,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="Q105" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -7017,10 +7014,10 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D106" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7029,7 +7026,7 @@
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H106">
         <v>105</v>
@@ -7039,10 +7036,10 @@
         <v>STREPTOMYCIN RESISTANCE DST</v>
       </c>
       <c r="J106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -7054,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="Q106" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -7065,10 +7062,10 @@
         <v>5</v>
       </c>
       <c r="C107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D107" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7077,7 +7074,7 @@
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H107">
         <v>106</v>
@@ -7087,10 +7084,10 @@
         <v>TERIZIDONE RESISTANCE DST</v>
       </c>
       <c r="J107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -7102,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="Q107" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -7113,10 +7110,10 @@
         <v>5</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D108" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7125,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H108">
         <v>107</v>
@@ -7135,10 +7132,10 @@
         <v>THIOACETAZONE RESISTANCE DST</v>
       </c>
       <c r="J108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -7150,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="Q108" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -7161,10 +7158,10 @@
         <v>5</v>
       </c>
       <c r="C109" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7173,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H109">
         <v>108</v>
@@ -7183,10 +7180,10 @@
         <v>VIOMYCIN RESISTANCE DST</v>
       </c>
       <c r="J109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -7198,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="Q109" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -7209,19 +7206,19 @@
         <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D110" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
         <v>40</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
-        <v>1</v>
-      </c>
-      <c r="G110" t="s">
-        <v>41</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -7231,7 +7228,7 @@
         <v xml:space="preserve">DATE COLLECTED </v>
       </c>
       <c r="J110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -7243,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="Q110" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -7254,10 +7251,10 @@
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7273,7 +7270,7 @@
         <v xml:space="preserve">INVESTIGATION DATE </v>
       </c>
       <c r="J111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -7285,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="Q111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -7296,11 +7293,11 @@
         <v>7</v>
       </c>
       <c r="C112" t="s">
+        <v>47</v>
+      </c>
+      <c r="D112" t="s">
         <v>48</v>
       </c>
-      <c r="D112" t="s">
-        <v>49</v>
-      </c>
       <c r="E112">
         <v>0</v>
       </c>
@@ -7308,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H112">
         <v>3</v>
@@ -7318,7 +7315,7 @@
         <v xml:space="preserve">LABORATORY INVESTIGATION NUMBER </v>
       </c>
       <c r="J112" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -7330,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="Q112" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -7341,19 +7338,19 @@
         <v>7</v>
       </c>
       <c r="C113" t="s">
+        <v>53</v>
+      </c>
+      <c r="D113" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
         <v>54</v>
-      </c>
-      <c r="D113" t="s">
-        <v>36</v>
-      </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
-      <c r="F113">
-        <v>1</v>
-      </c>
-      <c r="G113" t="s">
-        <v>55</v>
       </c>
       <c r="H113">
         <v>4</v>
@@ -7363,7 +7360,7 @@
         <v xml:space="preserve">PURPOSE OF INVESTIGATION </v>
       </c>
       <c r="J113" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -7375,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="Q113" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -7386,10 +7383,10 @@
         <v>7</v>
       </c>
       <c r="C114" t="s">
+        <v>56</v>
+      </c>
+      <c r="D114" t="s">
         <v>57</v>
-      </c>
-      <c r="D114" t="s">
-        <v>58</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7405,7 +7402,7 @@
         <v xml:space="preserve">REFERRING FACILITY </v>
       </c>
       <c r="J114" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -7417,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="Q114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -7428,19 +7425,19 @@
         <v>7</v>
       </c>
       <c r="C115" t="s">
+        <v>59</v>
+      </c>
+      <c r="D115" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
         <v>60</v>
-      </c>
-      <c r="D115" t="s">
-        <v>36</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-      <c r="F115">
-        <v>1</v>
-      </c>
-      <c r="G115" t="s">
-        <v>61</v>
       </c>
       <c r="H115">
         <v>6</v>
@@ -7450,7 +7447,7 @@
         <v xml:space="preserve">REQUESTING MEDICAL FACILITY </v>
       </c>
       <c r="J115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -7462,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="Q115" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -7473,10 +7470,10 @@
         <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7485,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H116">
         <v>7</v>
@@ -7495,7 +7492,7 @@
         <v xml:space="preserve">TUBERCULOSIS SAMPLE SOURCE </v>
       </c>
       <c r="J116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -7507,7 +7504,7 @@
         <v>0</v>
       </c>
       <c r="Q116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -7518,10 +7515,10 @@
         <v>7</v>
       </c>
       <c r="C117" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" t="s">
         <v>39</v>
-      </c>
-      <c r="D117" t="s">
-        <v>40</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7537,7 +7534,7 @@
         <v xml:space="preserve">DATE OF REQUEST FOR LABORATORY INVESTIGATION </v>
       </c>
       <c r="J117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7549,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="Q117" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -7560,19 +7557,19 @@
         <v>7</v>
       </c>
       <c r="C118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D118" t="s">
         <v>44</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
         <v>45</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118">
-        <v>1</v>
-      </c>
-      <c r="G118" t="s">
-        <v>46</v>
       </c>
       <c r="H118">
         <v>9</v>
@@ -7582,7 +7579,7 @@
         <v xml:space="preserve">LAB SPECIALIST NAME </v>
       </c>
       <c r="J118" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N118">
         <v>1</v>
@@ -7594,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="Q118" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -7605,19 +7602,19 @@
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D119" t="s">
+        <v>44</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
         <v>45</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>1</v>
-      </c>
-      <c r="G119" t="s">
-        <v>46</v>
       </c>
       <c r="H119">
         <v>10</v>
@@ -7627,7 +7624,7 @@
         <v xml:space="preserve">REFERRED BY </v>
       </c>
       <c r="J119" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -7639,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="Q119" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -7650,19 +7647,19 @@
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D120" t="s">
+        <v>44</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120" t="s">
         <v>45</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-      <c r="F120">
-        <v>1</v>
-      </c>
-      <c r="G120" t="s">
-        <v>46</v>
       </c>
       <c r="H120">
         <v>11</v>
@@ -7672,7 +7669,7 @@
         <v xml:space="preserve">TUBERCULOSIS SPECIMEN ID </v>
       </c>
       <c r="J120" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -7684,7 +7681,7 @@
         <v>0</v>
       </c>
       <c r="Q120" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -7695,19 +7692,19 @@
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D121" t="s">
+        <v>48</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" t="s">
         <v>49</v>
-      </c>
-      <c r="E121">
-        <v>0</v>
-      </c>
-      <c r="F121">
-        <v>1</v>
-      </c>
-      <c r="G121" t="s">
-        <v>50</v>
       </c>
       <c r="H121">
         <v>12</v>
@@ -7717,7 +7714,7 @@
         <v xml:space="preserve">MONTH OF TREATMENT </v>
       </c>
       <c r="J121" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -7729,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="Q121" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -7740,19 +7737,19 @@
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D122" t="s">
+        <v>48</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122" t="s">
         <v>49</v>
-      </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-      <c r="G122" t="s">
-        <v>50</v>
       </c>
       <c r="H122">
         <v>13</v>
@@ -7762,7 +7759,7 @@
         <v xml:space="preserve">PATIENT PROGRAM ID </v>
       </c>
       <c r="J122" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -7774,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="Q122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -7785,10 +7782,10 @@
         <v>7</v>
       </c>
       <c r="C123" t="s">
+        <v>98</v>
+      </c>
+      <c r="D123" t="s">
         <v>99</v>
-      </c>
-      <c r="D123" t="s">
-        <v>100</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7804,7 +7801,7 @@
         <v xml:space="preserve">DIRECT/INDIRECT </v>
       </c>
       <c r="J123" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L123" s="1"/>
       <c r="N123">
@@ -7817,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="Q123" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -7828,10 +7825,10 @@
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7840,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H124">
         <v>15</v>
@@ -7850,7 +7847,7 @@
         <v xml:space="preserve">TYPE OF ORGANISM </v>
       </c>
       <c r="J124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L124" s="1"/>
       <c r="N124">
@@ -7863,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="Q124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -7874,19 +7871,19 @@
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D125" t="s">
+        <v>44</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" t="s">
         <v>45</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-      <c r="F125">
-        <v>1</v>
-      </c>
-      <c r="G125" t="s">
-        <v>46</v>
       </c>
       <c r="H125">
         <v>16</v>
@@ -7896,7 +7893,7 @@
         <v xml:space="preserve">TYPE OF ORGANISM NON-CODED </v>
       </c>
       <c r="J125" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L125" s="1"/>
       <c r="N125">
@@ -7909,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="Q125" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -7920,19 +7917,19 @@
         <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D126" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="s">
         <v>49</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-      <c r="F126">
-        <v>1</v>
-      </c>
-      <c r="G126" t="s">
-        <v>50</v>
       </c>
       <c r="H126">
         <v>17</v>
@@ -7942,7 +7939,7 @@
         <v xml:space="preserve">COLONIES </v>
       </c>
       <c r="J126" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L126" s="1"/>
       <c r="N126">
@@ -7955,7 +7952,7 @@
         <v>0</v>
       </c>
       <c r="Q126" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -7966,19 +7963,19 @@
         <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D127" t="s">
+        <v>48</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" t="s">
         <v>49</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-      <c r="F127">
-        <v>1</v>
-      </c>
-      <c r="G127" t="s">
-        <v>50</v>
       </c>
       <c r="H127">
         <v>18</v>
@@ -7988,7 +7985,7 @@
         <v xml:space="preserve">CONCENTRATION </v>
       </c>
       <c r="J127" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L127" s="1"/>
       <c r="N127">
@@ -8001,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="Q127" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -8012,19 +8009,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D128" t="s">
+        <v>48</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
         <v>49</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-      <c r="G128" t="s">
-        <v>50</v>
       </c>
       <c r="H128">
         <v>19</v>
@@ -8034,7 +8031,7 @@
         <v xml:space="preserve">COLONIES IN CONTROL </v>
       </c>
       <c r="J128" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L128" s="1"/>
       <c r="N128">
@@ -8047,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="Q128" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -8058,19 +8055,19 @@
         <v>7</v>
       </c>
       <c r="C129" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D129" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="D129" t="s">
-        <v>36</v>
-      </c>
-      <c r="E129">
-        <v>0</v>
-      </c>
-      <c r="F129">
-        <v>1</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="H129">
         <v>20</v>
@@ -8080,7 +8077,7 @@
         <v xml:space="preserve">TUBERCULOSIS DRUG SENSITIVITY TEST METHOD </v>
       </c>
       <c r="J129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L129" s="1"/>
       <c r="N129">
@@ -8093,7 +8090,7 @@
         <v>0</v>
       </c>
       <c r="Q129" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -8104,10 +8101,10 @@
         <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D130" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8116,7 +8113,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H130">
         <v>21</v>
@@ -8126,7 +8123,7 @@
         <v xml:space="preserve">AMIKACIN RESISTANCE </v>
       </c>
       <c r="J130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L130" s="1"/>
       <c r="N130">
@@ -8139,7 +8136,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -8150,10 +8147,10 @@
         <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8162,7 +8159,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H131">
         <v>22</v>
@@ -8172,7 +8169,7 @@
         <v xml:space="preserve">BEDAQUILINE RESISTANCE </v>
       </c>
       <c r="J131" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L131" s="1"/>
       <c r="N131">
@@ -8185,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="Q131" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -8196,10 +8193,10 @@
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8208,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H132">
         <v>23</v>
@@ -8218,7 +8215,7 @@
         <v xml:space="preserve">CAPREOMYCIN RESISTANCE </v>
       </c>
       <c r="J132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L132" s="1"/>
       <c r="N132">
@@ -8231,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="Q132" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -8242,19 +8239,19 @@
         <v>7</v>
       </c>
       <c r="C133" t="s">
+        <v>130</v>
+      </c>
+      <c r="D133" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133" t="s">
         <v>131</v>
-      </c>
-      <c r="D133" t="s">
-        <v>36</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-      <c r="F133">
-        <v>1</v>
-      </c>
-      <c r="G133" t="s">
-        <v>132</v>
       </c>
       <c r="H133">
         <v>24</v>
@@ -8264,7 +8261,7 @@
         <v xml:space="preserve">CIPROFLOXACIN RESISTANCE </v>
       </c>
       <c r="J133" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L133" s="1"/>
       <c r="N133">
@@ -8277,7 +8274,7 @@
         <v>0</v>
       </c>
       <c r="Q133" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -8288,19 +8285,19 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
+        <v>132</v>
+      </c>
+      <c r="D134" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
         <v>133</v>
-      </c>
-      <c r="D134" t="s">
-        <v>36</v>
-      </c>
-      <c r="E134">
-        <v>0</v>
-      </c>
-      <c r="F134">
-        <v>1</v>
-      </c>
-      <c r="G134" t="s">
-        <v>134</v>
       </c>
       <c r="H134">
         <v>25</v>
@@ -8310,7 +8307,7 @@
         <v xml:space="preserve">CLARITHROMYCIN RESISTANCE </v>
       </c>
       <c r="J134" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L134" s="1"/>
       <c r="N134">
@@ -8323,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -8334,10 +8331,10 @@
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D135" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8346,7 +8343,7 @@
         <v>1</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H135">
         <v>27</v>
@@ -8356,7 +8353,7 @@
         <v xml:space="preserve">CLOFAZAMINE RESISTANCE </v>
       </c>
       <c r="J135" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L135" s="1"/>
       <c r="N135">
@@ -8369,7 +8366,7 @@
         <v>0</v>
       </c>
       <c r="Q135" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -8380,19 +8377,19 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
+        <v>134</v>
+      </c>
+      <c r="D136" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
         <v>135</v>
-      </c>
-      <c r="D136" t="s">
-        <v>36</v>
-      </c>
-      <c r="E136">
-        <v>0</v>
-      </c>
-      <c r="F136">
-        <v>1</v>
-      </c>
-      <c r="G136" t="s">
-        <v>136</v>
       </c>
       <c r="H136">
         <v>28</v>
@@ -8402,7 +8399,7 @@
         <v xml:space="preserve">CYCLOSERINE RESISTANCE </v>
       </c>
       <c r="J136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L136" s="1"/>
       <c r="N136">
@@ -8415,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="Q136" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -8426,10 +8423,10 @@
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D137" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -8438,7 +8435,7 @@
         <v>1</v>
       </c>
       <c r="G137" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H137">
         <v>29</v>
@@ -8448,7 +8445,7 @@
         <v xml:space="preserve">DELAMANID RESISTANCE </v>
       </c>
       <c r="J137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L137" s="1"/>
       <c r="N137">
@@ -8461,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="Q137" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -8472,19 +8469,19 @@
         <v>7</v>
       </c>
       <c r="C138" t="s">
+        <v>136</v>
+      </c>
+      <c r="D138" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
         <v>137</v>
-      </c>
-      <c r="D138" t="s">
-        <v>36</v>
-      </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
-      <c r="F138">
-        <v>1</v>
-      </c>
-      <c r="G138" t="s">
-        <v>138</v>
       </c>
       <c r="H138">
         <v>30</v>
@@ -8494,7 +8491,7 @@
         <v xml:space="preserve">ETHAMBUTOL RESISTANCE </v>
       </c>
       <c r="J138" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L138" s="1"/>
       <c r="N138">
@@ -8507,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="Q138" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -8518,10 +8515,10 @@
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8530,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H139">
         <v>31</v>
@@ -8540,7 +8537,7 @@
         <v xml:space="preserve">ETHIONAMIDE RESISTANCE </v>
       </c>
       <c r="J139" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L139" s="1"/>
       <c r="N139">
@@ -8553,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="Q139" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -8564,10 +8561,10 @@
         <v>7</v>
       </c>
       <c r="C140" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8576,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H140">
         <v>32</v>
@@ -8586,7 +8583,7 @@
         <v xml:space="preserve">GATIFLOXACIN RESISTANCE </v>
       </c>
       <c r="J140" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L140" s="1"/>
       <c r="N140">
@@ -8599,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="Q140" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -8610,10 +8607,10 @@
         <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8622,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H141">
         <v>33</v>
@@ -8632,7 +8629,7 @@
         <v xml:space="preserve">ISONIAZID RESISTANCE </v>
       </c>
       <c r="J141" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L141" s="1"/>
       <c r="N141">
@@ -8645,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="Q141" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -8656,10 +8653,10 @@
         <v>7</v>
       </c>
       <c r="C142" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8668,7 +8665,7 @@
         <v>1</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H142">
         <v>35</v>
@@ -8678,7 +8675,7 @@
         <v xml:space="preserve">KANAMYCIN RESISTANCE </v>
       </c>
       <c r="J142" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L142" s="1"/>
       <c r="N142">
@@ -8691,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="Q142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -8702,10 +8699,10 @@
         <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8714,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H143">
         <v>36</v>
@@ -8724,7 +8721,7 @@
         <v xml:space="preserve">LEVOFLOXACIN RESISTANCE </v>
       </c>
       <c r="J143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L143" s="1"/>
       <c r="N143">
@@ -8737,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="Q143" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -8748,10 +8745,10 @@
         <v>7</v>
       </c>
       <c r="C144" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8760,7 +8757,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H144">
         <v>47</v>
@@ -8770,7 +8767,7 @@
         <v xml:space="preserve">LINEZOLID RESISTANCE </v>
       </c>
       <c r="J144" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L144" s="1"/>
       <c r="N144">
@@ -8783,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="Q144" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -8794,10 +8791,10 @@
         <v>7</v>
       </c>
       <c r="C145" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8806,7 +8803,7 @@
         <v>1</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H145">
         <v>38</v>
@@ -8816,7 +8813,7 @@
         <v xml:space="preserve">MOXIFLOXACIN RESISTANCE </v>
       </c>
       <c r="J145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L145" s="1"/>
       <c r="N145">
@@ -8829,7 +8826,7 @@
         <v>0</v>
       </c>
       <c r="Q145" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -8840,10 +8837,10 @@
         <v>7</v>
       </c>
       <c r="C146" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -8852,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H146">
         <v>39</v>
@@ -8862,7 +8859,7 @@
         <v xml:space="preserve">OFLOXACIN RESISTANCE </v>
       </c>
       <c r="J146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L146" s="1"/>
       <c r="N146">
@@ -8875,7 +8872,7 @@
         <v>0</v>
       </c>
       <c r="Q146" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -8886,10 +8883,10 @@
         <v>7</v>
       </c>
       <c r="C147" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -8898,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H147">
         <v>40</v>
@@ -8908,7 +8905,7 @@
         <v xml:space="preserve">OTHER RESISTANCE </v>
       </c>
       <c r="J147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L147" s="1"/>
       <c r="N147">
@@ -8921,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="Q147" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -8932,10 +8929,10 @@
         <v>7</v>
       </c>
       <c r="C148" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -8944,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H148">
         <v>41</v>
@@ -8954,7 +8951,7 @@
         <v xml:space="preserve">P-AMINOSALICY RESISTANCE </v>
       </c>
       <c r="J148" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L148" s="1"/>
       <c r="N148">
@@ -8967,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="Q148" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -8978,10 +8975,10 @@
         <v>7</v>
       </c>
       <c r="C149" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -8990,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H149">
         <v>42</v>
@@ -9000,7 +8997,7 @@
         <v xml:space="preserve">PROTHIONAMIDE RESISTANCE </v>
       </c>
       <c r="J149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L149" s="1"/>
       <c r="N149">
@@ -9013,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="Q149" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -9024,10 +9021,10 @@
         <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -9036,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H150">
         <v>43</v>
@@ -9046,7 +9043,7 @@
         <v xml:space="preserve">PYRAZINAMIDE RESISTANCE </v>
       </c>
       <c r="J150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L150" s="1"/>
       <c r="N150">
@@ -9059,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="Q150" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -9070,10 +9067,10 @@
         <v>7</v>
       </c>
       <c r="C151" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9082,7 +9079,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H151">
         <v>44</v>
@@ -9092,7 +9089,7 @@
         <v xml:space="preserve">PYRIDOXINE RESISTANCE </v>
       </c>
       <c r="J151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L151" s="1"/>
       <c r="N151">
@@ -9105,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="Q151" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -9116,10 +9113,10 @@
         <v>7</v>
       </c>
       <c r="C152" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -9128,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H152">
         <v>45</v>
@@ -9138,7 +9135,7 @@
         <v xml:space="preserve">RIFABUTIN RESISTANCE </v>
       </c>
       <c r="J152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L152" s="1"/>
       <c r="N152">
@@ -9151,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="Q152" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -9162,10 +9159,10 @@
         <v>7</v>
       </c>
       <c r="C153" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -9174,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H153">
         <v>46</v>
@@ -9184,7 +9181,7 @@
         <v xml:space="preserve">RIFAMPICIN RESISTANCE </v>
       </c>
       <c r="J153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L153" s="1"/>
       <c r="N153">
@@ -9197,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="Q153" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -9208,10 +9205,10 @@
         <v>7</v>
       </c>
       <c r="C154" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9220,7 +9217,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H154">
         <v>37</v>
@@ -9230,7 +9227,7 @@
         <v xml:space="preserve">STREPTOMYCIN RESISTANCE </v>
       </c>
       <c r="J154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L154" s="1"/>
       <c r="N154">
@@ -9243,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="Q154" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -9254,10 +9251,10 @@
         <v>7</v>
       </c>
       <c r="C155" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -9266,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H155">
         <v>38</v>
@@ -9276,7 +9273,7 @@
         <v xml:space="preserve">TERIZIDONE RESISTANCE </v>
       </c>
       <c r="J155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L155" s="1"/>
       <c r="N155">
@@ -9289,7 +9286,7 @@
         <v>0</v>
       </c>
       <c r="Q155" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -9300,10 +9297,10 @@
         <v>7</v>
       </c>
       <c r="C156" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -9312,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H156">
         <v>39</v>
@@ -9322,7 +9319,7 @@
         <v xml:space="preserve">THIOACETAZONE RESISTANCE </v>
       </c>
       <c r="J156" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L156" s="1"/>
       <c r="N156">
@@ -9335,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="Q156" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -9346,10 +9343,10 @@
         <v>7</v>
       </c>
       <c r="C157" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -9358,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H157">
         <v>40</v>
@@ -9368,7 +9365,7 @@
         <v xml:space="preserve">VIOMYCIN RESISTANCE </v>
       </c>
       <c r="J157" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L157" s="1"/>
       <c r="N157">
@@ -9381,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="Q157" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -9392,19 +9389,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D158" t="s">
+        <v>39</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158" t="s">
         <v>40</v>
-      </c>
-      <c r="E158">
-        <v>0</v>
-      </c>
-      <c r="F158">
-        <v>1</v>
-      </c>
-      <c r="G158" t="s">
-        <v>41</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -9414,7 +9411,7 @@
         <v xml:space="preserve">DATE COLLECTED </v>
       </c>
       <c r="J158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N158">
         <v>1</v>
@@ -9426,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="Q158" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -9437,10 +9434,10 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -9456,7 +9453,7 @@
         <v xml:space="preserve">INVESTIGATION DATE </v>
       </c>
       <c r="J159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N159">
         <v>1</v>
@@ -9468,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="Q159" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -9479,11 +9476,11 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>47</v>
+      </c>
+      <c r="D160" t="s">
         <v>48</v>
       </c>
-      <c r="D160" t="s">
-        <v>49</v>
-      </c>
       <c r="E160">
         <v>0</v>
       </c>
@@ -9491,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H160">
         <v>3</v>
@@ -9501,7 +9498,7 @@
         <v xml:space="preserve">LABORATORY INVESTIGATION NUMBER </v>
       </c>
       <c r="J160" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N160">
         <v>1</v>
@@ -9513,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="Q160" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -9524,19 +9521,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>53</v>
+      </c>
+      <c r="D161" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161" t="s">
         <v>54</v>
-      </c>
-      <c r="D161" t="s">
-        <v>36</v>
-      </c>
-      <c r="E161">
-        <v>0</v>
-      </c>
-      <c r="F161">
-        <v>1</v>
-      </c>
-      <c r="G161" t="s">
-        <v>55</v>
       </c>
       <c r="H161">
         <v>4</v>
@@ -9546,7 +9543,7 @@
         <v xml:space="preserve">PURPOSE OF INVESTIGATION </v>
       </c>
       <c r="J161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N161">
         <v>1</v>
@@ -9558,7 +9555,7 @@
         <v>0</v>
       </c>
       <c r="Q161" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -9569,10 +9566,10 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>56</v>
+      </c>
+      <c r="D162" t="s">
         <v>57</v>
-      </c>
-      <c r="D162" t="s">
-        <v>58</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -9588,7 +9585,7 @@
         <v xml:space="preserve">REFERRING FACILITY </v>
       </c>
       <c r="J162" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N162">
         <v>1</v>
@@ -9600,7 +9597,7 @@
         <v>0</v>
       </c>
       <c r="Q162" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -9611,19 +9608,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>59</v>
+      </c>
+      <c r="D163" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163" t="s">
         <v>60</v>
-      </c>
-      <c r="D163" t="s">
-        <v>36</v>
-      </c>
-      <c r="E163">
-        <v>0</v>
-      </c>
-      <c r="F163">
-        <v>1</v>
-      </c>
-      <c r="G163" t="s">
-        <v>61</v>
       </c>
       <c r="H163">
         <v>6</v>
@@ -9633,7 +9630,7 @@
         <v xml:space="preserve">REQUESTING MEDICAL FACILITY </v>
       </c>
       <c r="J163" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N163">
         <v>1</v>
@@ -9645,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="Q163" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -9656,10 +9653,10 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D164" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -9668,7 +9665,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H164">
         <v>7</v>
@@ -9678,7 +9675,7 @@
         <v xml:space="preserve">TUBERCULOSIS SAMPLE SOURCE </v>
       </c>
       <c r="J164" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N164">
         <v>1</v>
@@ -9690,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="Q164" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -9701,10 +9698,10 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>38</v>
+      </c>
+      <c r="D165" t="s">
         <v>39</v>
-      </c>
-      <c r="D165" t="s">
-        <v>40</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -9720,7 +9717,7 @@
         <v xml:space="preserve">DATE OF REQUEST FOR LABORATORY INVESTIGATION </v>
       </c>
       <c r="J165" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N165">
         <v>1</v>
@@ -9732,7 +9729,7 @@
         <v>0</v>
       </c>
       <c r="Q165" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -9743,19 +9740,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>43</v>
+      </c>
+      <c r="D166" t="s">
         <v>44</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166" t="s">
         <v>45</v>
-      </c>
-      <c r="E166">
-        <v>0</v>
-      </c>
-      <c r="F166">
-        <v>1</v>
-      </c>
-      <c r="G166" t="s">
-        <v>46</v>
       </c>
       <c r="H166">
         <v>9</v>
@@ -9765,7 +9762,7 @@
         <v xml:space="preserve">LAB SPECIALIST NAME </v>
       </c>
       <c r="J166" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N166">
         <v>1</v>
@@ -9777,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="Q166" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -9788,19 +9785,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D167" t="s">
+        <v>44</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167" t="s">
         <v>45</v>
-      </c>
-      <c r="E167">
-        <v>0</v>
-      </c>
-      <c r="F167">
-        <v>1</v>
-      </c>
-      <c r="G167" t="s">
-        <v>46</v>
       </c>
       <c r="H167">
         <v>10</v>
@@ -9810,7 +9807,7 @@
         <v xml:space="preserve">REFERRED BY </v>
       </c>
       <c r="J167" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N167">
         <v>1</v>
@@ -9822,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="Q167" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -9833,19 +9830,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D168" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168" t="s">
         <v>45</v>
-      </c>
-      <c r="E168">
-        <v>0</v>
-      </c>
-      <c r="F168">
-        <v>1</v>
-      </c>
-      <c r="G168" t="s">
-        <v>46</v>
       </c>
       <c r="H168">
         <v>11</v>
@@ -9855,7 +9852,7 @@
         <v xml:space="preserve">TUBERCULOSIS SPECIMEN ID </v>
       </c>
       <c r="J168" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N168">
         <v>1</v>
@@ -9867,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="Q168" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -9878,19 +9875,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D169" t="s">
+        <v>48</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="s">
         <v>49</v>
-      </c>
-      <c r="E169">
-        <v>0</v>
-      </c>
-      <c r="F169">
-        <v>1</v>
-      </c>
-      <c r="G169" t="s">
-        <v>50</v>
       </c>
       <c r="H169">
         <v>12</v>
@@ -9900,7 +9897,7 @@
         <v xml:space="preserve">MONTH OF TREATMENT </v>
       </c>
       <c r="J169" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N169">
         <v>1</v>
@@ -9912,7 +9909,7 @@
         <v>0</v>
       </c>
       <c r="Q169" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -9923,19 +9920,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D170" t="s">
+        <v>48</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170" t="s">
         <v>49</v>
-      </c>
-      <c r="E170">
-        <v>0</v>
-      </c>
-      <c r="F170">
-        <v>1</v>
-      </c>
-      <c r="G170" t="s">
-        <v>50</v>
       </c>
       <c r="H170">
         <v>13</v>
@@ -9945,7 +9942,7 @@
         <v xml:space="preserve">PATIENT PROGRAM ID </v>
       </c>
       <c r="J170" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N170">
         <v>1</v>
@@ -9957,7 +9954,7 @@
         <v>0</v>
       </c>
       <c r="Q170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -9968,10 +9965,10 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>98</v>
+      </c>
+      <c r="D171" t="s">
         <v>99</v>
-      </c>
-      <c r="D171" t="s">
-        <v>100</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -9987,7 +9984,7 @@
         <v xml:space="preserve">DIRECT/INDIRECT </v>
       </c>
       <c r="J171" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L171" s="1"/>
       <c r="N171">
@@ -10000,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="Q171" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -10011,10 +10008,10 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D172" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -10023,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="G172" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H172">
         <v>15</v>
@@ -10033,7 +10030,7 @@
         <v xml:space="preserve">TYPE OF ORGANISM </v>
       </c>
       <c r="J172" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L172" s="1"/>
       <c r="N172">
@@ -10046,7 +10043,7 @@
         <v>0</v>
       </c>
       <c r="Q172" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -10057,19 +10054,19 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D173" t="s">
+        <v>44</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173" t="s">
         <v>45</v>
-      </c>
-      <c r="E173">
-        <v>0</v>
-      </c>
-      <c r="F173">
-        <v>1</v>
-      </c>
-      <c r="G173" t="s">
-        <v>46</v>
       </c>
       <c r="H173">
         <v>16</v>
@@ -10079,7 +10076,7 @@
         <v xml:space="preserve">TYPE OF ORGANISM NON-CODED </v>
       </c>
       <c r="J173" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L173" s="1"/>
       <c r="N173">
@@ -10092,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="Q173" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -10103,19 +10100,19 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D174" t="s">
+        <v>48</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174" t="s">
         <v>49</v>
-      </c>
-      <c r="E174">
-        <v>0</v>
-      </c>
-      <c r="F174">
-        <v>1</v>
-      </c>
-      <c r="G174" t="s">
-        <v>50</v>
       </c>
       <c r="H174">
         <v>17</v>
@@ -10125,7 +10122,7 @@
         <v xml:space="preserve">COLONIES </v>
       </c>
       <c r="J174" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L174" s="1"/>
       <c r="N174">
@@ -10138,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="Q174" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -10149,19 +10146,19 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D175" t="s">
+        <v>48</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175" t="s">
         <v>49</v>
-      </c>
-      <c r="E175">
-        <v>0</v>
-      </c>
-      <c r="F175">
-        <v>1</v>
-      </c>
-      <c r="G175" t="s">
-        <v>50</v>
       </c>
       <c r="H175">
         <v>18</v>
@@ -10171,7 +10168,7 @@
         <v xml:space="preserve">CONCENTRATION </v>
       </c>
       <c r="J175" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L175" s="1"/>
       <c r="N175">
@@ -10184,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="Q175" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -10195,19 +10192,19 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D176" t="s">
+        <v>48</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176" t="s">
         <v>49</v>
-      </c>
-      <c r="E176">
-        <v>0</v>
-      </c>
-      <c r="F176">
-        <v>1</v>
-      </c>
-      <c r="G176" t="s">
-        <v>50</v>
       </c>
       <c r="H176">
         <v>19</v>
@@ -10217,7 +10214,7 @@
         <v xml:space="preserve">COLONIES IN CONTROL </v>
       </c>
       <c r="J176" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L176" s="1"/>
       <c r="N176">
@@ -10230,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="Q176" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -10241,19 +10238,19 @@
         <v>8</v>
       </c>
       <c r="C177" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D177" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="D177" t="s">
-        <v>36</v>
-      </c>
-      <c r="E177">
-        <v>0</v>
-      </c>
-      <c r="F177">
-        <v>1</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="H177">
         <v>20</v>
@@ -10263,7 +10260,7 @@
         <v xml:space="preserve">TUBERCULOSIS DRUG SENSITIVITY TEST METHOD </v>
       </c>
       <c r="J177" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L177" s="1"/>
       <c r="N177">
@@ -10276,7 +10273,7 @@
         <v>0</v>
       </c>
       <c r="Q177" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -10287,10 +10284,10 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D178" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -10299,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H178">
         <v>21</v>
@@ -10309,7 +10306,7 @@
         <v xml:space="preserve">AMIKACIN RESISTANCE </v>
       </c>
       <c r="J178" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L178" s="1"/>
       <c r="N178">
@@ -10322,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="Q178" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -10333,10 +10330,10 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D179" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -10345,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H179">
         <v>22</v>
@@ -10355,7 +10352,7 @@
         <v xml:space="preserve">BEDAQUILINE RESISTANCE </v>
       </c>
       <c r="J179" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L179" s="1"/>
       <c r="N179">
@@ -10368,7 +10365,7 @@
         <v>0</v>
       </c>
       <c r="Q179" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -10379,10 +10376,10 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D180" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -10391,7 +10388,7 @@
         <v>1</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H180">
         <v>23</v>
@@ -10401,7 +10398,7 @@
         <v xml:space="preserve">CAPREOMYCIN RESISTANCE </v>
       </c>
       <c r="J180" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L180" s="1"/>
       <c r="N180">
@@ -10414,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="Q180" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -10425,19 +10422,19 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
+        <v>130</v>
+      </c>
+      <c r="D181" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181" t="s">
         <v>131</v>
-      </c>
-      <c r="D181" t="s">
-        <v>36</v>
-      </c>
-      <c r="E181">
-        <v>0</v>
-      </c>
-      <c r="F181">
-        <v>1</v>
-      </c>
-      <c r="G181" t="s">
-        <v>132</v>
       </c>
       <c r="H181">
         <v>24</v>
@@ -10447,7 +10444,7 @@
         <v xml:space="preserve">CIPROFLOXACIN RESISTANCE </v>
       </c>
       <c r="J181" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L181" s="1"/>
       <c r="N181">
@@ -10460,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="Q181" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -10471,19 +10468,19 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D182" t="s">
+        <v>35</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182" t="s">
         <v>133</v>
-      </c>
-      <c r="D182" t="s">
-        <v>36</v>
-      </c>
-      <c r="E182">
-        <v>0</v>
-      </c>
-      <c r="F182">
-        <v>1</v>
-      </c>
-      <c r="G182" t="s">
-        <v>134</v>
       </c>
       <c r="H182">
         <v>25</v>
@@ -10493,7 +10490,7 @@
         <v xml:space="preserve">CLARITHROMYCIN RESISTANCE </v>
       </c>
       <c r="J182" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L182" s="1"/>
       <c r="N182">
@@ -10506,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="Q182" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -10517,10 +10514,10 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D183" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -10529,7 +10526,7 @@
         <v>1</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H183">
         <v>27</v>
@@ -10539,7 +10536,7 @@
         <v xml:space="preserve">CLOFAZAMINE RESISTANCE </v>
       </c>
       <c r="J183" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L183" s="1"/>
       <c r="N183">
@@ -10552,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="Q183" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -10563,19 +10560,19 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
+        <v>134</v>
+      </c>
+      <c r="D184" t="s">
+        <v>35</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184" t="s">
         <v>135</v>
-      </c>
-      <c r="D184" t="s">
-        <v>36</v>
-      </c>
-      <c r="E184">
-        <v>0</v>
-      </c>
-      <c r="F184">
-        <v>1</v>
-      </c>
-      <c r="G184" t="s">
-        <v>136</v>
       </c>
       <c r="H184">
         <v>28</v>
@@ -10585,7 +10582,7 @@
         <v xml:space="preserve">CYCLOSERINE RESISTANCE </v>
       </c>
       <c r="J184" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L184" s="1"/>
       <c r="N184">
@@ -10598,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="Q184" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -10609,10 +10606,10 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D185" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -10621,7 +10618,7 @@
         <v>1</v>
       </c>
       <c r="G185" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H185">
         <v>29</v>
@@ -10631,7 +10628,7 @@
         <v xml:space="preserve">DELAMANID RESISTANCE </v>
       </c>
       <c r="J185" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L185" s="1"/>
       <c r="N185">
@@ -10644,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="Q185" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -10655,19 +10652,19 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
+        <v>136</v>
+      </c>
+      <c r="D186" t="s">
+        <v>35</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186" t="s">
         <v>137</v>
-      </c>
-      <c r="D186" t="s">
-        <v>36</v>
-      </c>
-      <c r="E186">
-        <v>0</v>
-      </c>
-      <c r="F186">
-        <v>1</v>
-      </c>
-      <c r="G186" t="s">
-        <v>138</v>
       </c>
       <c r="H186">
         <v>30</v>
@@ -10677,7 +10674,7 @@
         <v xml:space="preserve">ETHAMBUTOL RESISTANCE </v>
       </c>
       <c r="J186" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L186" s="1"/>
       <c r="N186">
@@ -10690,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="Q186" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -10701,10 +10698,10 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D187" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -10713,7 +10710,7 @@
         <v>1</v>
       </c>
       <c r="G187" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H187">
         <v>31</v>
@@ -10723,7 +10720,7 @@
         <v xml:space="preserve">ETHIONAMIDE RESISTANCE </v>
       </c>
       <c r="J187" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L187" s="1"/>
       <c r="N187">
@@ -10736,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="Q187" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -10747,10 +10744,10 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D188" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -10759,7 +10756,7 @@
         <v>1</v>
       </c>
       <c r="G188" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H188">
         <v>32</v>
@@ -10769,7 +10766,7 @@
         <v xml:space="preserve">GATIFLOXACIN RESISTANCE </v>
       </c>
       <c r="J188" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L188" s="1"/>
       <c r="N188">
@@ -10782,7 +10779,7 @@
         <v>0</v>
       </c>
       <c r="Q188" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -10793,10 +10790,10 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D189" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -10805,7 +10802,7 @@
         <v>1</v>
       </c>
       <c r="G189" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H189">
         <v>33</v>
@@ -10815,7 +10812,7 @@
         <v xml:space="preserve">ISONIAZID RESISTANCE </v>
       </c>
       <c r="J189" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L189" s="1"/>
       <c r="N189">
@@ -10828,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="Q189" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -10839,10 +10836,10 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D190" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -10851,7 +10848,7 @@
         <v>1</v>
       </c>
       <c r="G190" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H190">
         <v>35</v>
@@ -10861,7 +10858,7 @@
         <v xml:space="preserve">KANAMYCIN RESISTANCE </v>
       </c>
       <c r="J190" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L190" s="1"/>
       <c r="N190">
@@ -10874,7 +10871,7 @@
         <v>0</v>
       </c>
       <c r="Q190" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -10885,10 +10882,10 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D191" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -10897,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H191">
         <v>36</v>
@@ -10907,7 +10904,7 @@
         <v xml:space="preserve">LEVOFLOXACIN RESISTANCE </v>
       </c>
       <c r="J191" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L191" s="1"/>
       <c r="N191">
@@ -10920,7 +10917,7 @@
         <v>0</v>
       </c>
       <c r="Q191" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -10931,10 +10928,10 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D192" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -10943,7 +10940,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H192">
         <v>47</v>
@@ -10953,7 +10950,7 @@
         <v xml:space="preserve">LINEZOLID RESISTANCE </v>
       </c>
       <c r="J192" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L192" s="1"/>
       <c r="N192">
@@ -10966,7 +10963,7 @@
         <v>0</v>
       </c>
       <c r="Q192" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -10977,10 +10974,10 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D193" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -10989,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H193">
         <v>38</v>
@@ -10999,7 +10996,7 @@
         <v xml:space="preserve">MOXIFLOXACIN RESISTANCE </v>
       </c>
       <c r="J193" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L193" s="1"/>
       <c r="N193">
@@ -11012,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="Q193" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -11023,10 +11020,10 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D194" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -11035,7 +11032,7 @@
         <v>1</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H194">
         <v>39</v>
@@ -11045,7 +11042,7 @@
         <v xml:space="preserve">OFLOXACIN RESISTANCE </v>
       </c>
       <c r="J194" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L194" s="1"/>
       <c r="N194">
@@ -11058,7 +11055,7 @@
         <v>0</v>
       </c>
       <c r="Q194" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -11069,10 +11066,10 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D195" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -11081,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H195">
         <v>40</v>
@@ -11091,7 +11088,7 @@
         <v xml:space="preserve">OTHER RESISTANCE </v>
       </c>
       <c r="J195" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L195" s="1"/>
       <c r="N195">
@@ -11104,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="Q195" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -11115,10 +11112,10 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D196" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -11127,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H196">
         <v>41</v>
@@ -11137,7 +11134,7 @@
         <v xml:space="preserve">P-AMINOSALICY RESISTANCE </v>
       </c>
       <c r="J196" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L196" s="1"/>
       <c r="N196">
@@ -11150,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="Q196" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -11161,10 +11158,10 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D197" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -11173,7 +11170,7 @@
         <v>1</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H197">
         <v>42</v>
@@ -11183,7 +11180,7 @@
         <v xml:space="preserve">PROTHIONAMIDE RESISTANCE </v>
       </c>
       <c r="J197" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L197" s="1"/>
       <c r="N197">
@@ -11196,7 +11193,7 @@
         <v>0</v>
       </c>
       <c r="Q197" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -11207,10 +11204,10 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D198" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -11219,7 +11216,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H198">
         <v>43</v>
@@ -11229,7 +11226,7 @@
         <v xml:space="preserve">PYRAZINAMIDE RESISTANCE </v>
       </c>
       <c r="J198" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L198" s="1"/>
       <c r="N198">
@@ -11242,7 +11239,7 @@
         <v>0</v>
       </c>
       <c r="Q198" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -11253,10 +11250,10 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D199" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -11265,7 +11262,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H199">
         <v>44</v>
@@ -11275,7 +11272,7 @@
         <v xml:space="preserve">PYRIDOXINE RESISTANCE </v>
       </c>
       <c r="J199" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L199" s="1"/>
       <c r="N199">
@@ -11288,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="Q199" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -11299,10 +11296,10 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D200" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -11311,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="G200" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H200">
         <v>45</v>
@@ -11321,7 +11318,7 @@
         <v xml:space="preserve">RIFABUTIN RESISTANCE </v>
       </c>
       <c r="J200" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L200" s="1"/>
       <c r="N200">
@@ -11334,7 +11331,7 @@
         <v>0</v>
       </c>
       <c r="Q200" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -11345,10 +11342,10 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D201" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -11357,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="G201" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H201">
         <v>46</v>
@@ -11367,7 +11364,7 @@
         <v xml:space="preserve">RIFAMPICIN RESISTANCE </v>
       </c>
       <c r="J201" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L201" s="1"/>
       <c r="N201">
@@ -11380,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="Q201" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -11391,10 +11388,10 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D202" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -11403,7 +11400,7 @@
         <v>1</v>
       </c>
       <c r="G202" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H202">
         <v>37</v>
@@ -11413,7 +11410,7 @@
         <v xml:space="preserve">STREPTOMYCIN RESISTANCE </v>
       </c>
       <c r="J202" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L202" s="1"/>
       <c r="N202">
@@ -11426,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="Q202" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -11437,10 +11434,10 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D203" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -11449,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H203">
         <v>38</v>
@@ -11459,7 +11456,7 @@
         <v xml:space="preserve">TERIZIDONE RESISTANCE </v>
       </c>
       <c r="J203" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L203" s="1"/>
       <c r="N203">
@@ -11472,7 +11469,7 @@
         <v>0</v>
       </c>
       <c r="Q203" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -11483,10 +11480,10 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D204" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -11495,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H204">
         <v>39</v>
@@ -11505,7 +11502,7 @@
         <v xml:space="preserve">THIOACETAZONE RESISTANCE </v>
       </c>
       <c r="J204" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L204" s="1"/>
       <c r="N204">
@@ -11518,7 +11515,7 @@
         <v>0</v>
       </c>
       <c r="Q204" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -11529,10 +11526,10 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D205" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -11541,7 +11538,7 @@
         <v>1</v>
       </c>
       <c r="G205" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H205">
         <v>40</v>
@@ -11551,7 +11548,7 @@
         <v xml:space="preserve">VIOMYCIN RESISTANCE </v>
       </c>
       <c r="J205" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L205" s="1"/>
       <c r="N205">
@@ -11564,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="Q205" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/resources/commonlab.xlsx
+++ b/resources/commonlab.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="442">
   <si>
     <t>uuid</t>
   </si>
@@ -1288,6 +1288,93 @@
   </si>
   <si>
     <t>95b09185-3928-11ee-9784-e86a64440f18</t>
+  </si>
+  <si>
+    <t>XPERT ULTRA</t>
+  </si>
+  <si>
+    <t>c91fb03b-acaf-4a3c-9a5b-3d32e4ac4d34</t>
+  </si>
+  <si>
+    <t>159f8b31-0c0a-4377-bea9-667a72a949b7</t>
+  </si>
+  <si>
+    <t>cedb082c-3a94-48f6-a192-fda9f2c48afd</t>
+  </si>
+  <si>
+    <t>XPERT ULTRA MTB BURDEN</t>
+  </si>
+  <si>
+    <t>ab70a74d-2bcd-4deb-abe7-d3dc9058edaf</t>
+  </si>
+  <si>
+    <t>3fb27302-f1ca-477a-9306-58bba806cfd8</t>
+  </si>
+  <si>
+    <t>686387e4-af27-4442-af41-395e72f1f712</t>
+  </si>
+  <si>
+    <t>ec9b4609-7ea5-461e-9aa6-bd515d230d52</t>
+  </si>
+  <si>
+    <t>479844a7-745f-4d40-9fff-dd254dfd8935</t>
+  </si>
+  <si>
+    <t>b28d58fc-a765-4a63-9d43-538c1880a413</t>
+  </si>
+  <si>
+    <t>e69a0ce4-18c9-49f9-bcfb-713447214933</t>
+  </si>
+  <si>
+    <t>fd5ef525-8f47-4553-836b-a00289e2e2a0</t>
+  </si>
+  <si>
+    <t>XPERT XDR</t>
+  </si>
+  <si>
+    <t>f516fc8a-2a06-4ffa-bbcb-1f69d855dd14</t>
+  </si>
+  <si>
+    <t>304cf8f8-2424-4070-a7aa-721b971d0894</t>
+  </si>
+  <si>
+    <t>a3d9d7f6-0cea-4fe9-968e-5778438e8226</t>
+  </si>
+  <si>
+    <t>89d6f422-6653-413f-9d44-be07095d383e</t>
+  </si>
+  <si>
+    <t>f6ca29a8-c6d5-49b9-b25d-e0a1e20de760</t>
+  </si>
+  <si>
+    <t>KM/AM/CM RESULT</t>
+  </si>
+  <si>
+    <t>6e350688-a9e8-4685-b614-b5951542c6d6</t>
+  </si>
+  <si>
+    <t>ETHIONAMIDE RESULT</t>
+  </si>
+  <si>
+    <t>f4cde26f-614b-4015-8c20-497bc90f7de1</t>
+  </si>
+  <si>
+    <t>1ad71659-6d1d-4e86-a489-8c12e70b13a9</t>
+  </si>
+  <si>
+    <t>c48f9814-6c04-471b-adda-713625e6678e</t>
+  </si>
+  <si>
+    <t>97866288-9749-476d-862f-dd9a09076186</t>
+  </si>
+  <si>
+    <t>de67a5c3-a093-419e-96ea-f376530824f5</t>
+  </si>
+  <si>
+    <t>75a82d0c-a2dc-49e0-9d27-3a42950713df</t>
+  </si>
+  <si>
+    <t>f399e490-ed5a-474f-a755-63d22092e05f</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91536433-8730-4EA0-BCCE-0E80DA08A6A5}">
-  <dimension ref="A1:Q205"/>
+  <dimension ref="A1:Q227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -11564,9 +11651,1087 @@
         <v>360</v>
       </c>
     </row>
+    <row r="206" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>5</v>
+      </c>
+      <c r="C206" t="s">
+        <v>34</v>
+      </c>
+      <c r="D206" t="s">
+        <v>35</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206" t="s">
+        <v>36</v>
+      </c>
+      <c r="H206">
+        <v>109</v>
+      </c>
+      <c r="I206" t="str">
+        <f>C206 &amp; " " &amp;L206</f>
+        <v xml:space="preserve">APPEARANCE OF SPECIMEN XPERT ULTRA</v>
+      </c>
+      <c r="J206" t="s">
+        <v>37</v>
+      </c>
+      <c r="K206"/>
+      <c r="L206" t="s">
+        <v>413</v>
+      </c>
+      <c r="M206"/>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>5</v>
+      </c>
+      <c r="C207" t="s">
+        <v>51</v>
+      </c>
+      <c r="D207" t="s">
+        <v>35</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" t="s">
+        <v>52</v>
+      </c>
+      <c r="H207">
+        <v>110</v>
+      </c>
+      <c r="I207" t="str">
+        <f>C207 &amp; " " &amp;L207</f>
+        <v xml:space="preserve">MTB RESULT XPERT ULTRA</v>
+      </c>
+      <c r="J207" t="s">
+        <v>37</v>
+      </c>
+      <c r="K207"/>
+      <c r="L207" t="s">
+        <v>413</v>
+      </c>
+      <c r="M207"/>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P207">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>5</v>
+      </c>
+      <c r="C208" t="s">
+        <v>85</v>
+      </c>
+      <c r="D208" t="s">
+        <v>44</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208" t="s">
+        <v>45</v>
+      </c>
+      <c r="H208">
+        <v>111</v>
+      </c>
+      <c r="I208" t="str">
+        <f>C208 &amp; " " &amp;L208</f>
+        <v xml:space="preserve">ERROR CODE XPERT ULTRA</v>
+      </c>
+      <c r="J208" t="s">
+        <v>46</v>
+      </c>
+      <c r="K208"/>
+      <c r="L208" t="s">
+        <v>413</v>
+      </c>
+      <c r="M208"/>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P208">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>5</v>
+      </c>
+      <c r="C209" t="s">
+        <v>417</v>
+      </c>
+      <c r="D209" t="s">
+        <v>35</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209" t="s">
+        <v>418</v>
+      </c>
+      <c r="H209">
+        <v>112</v>
+      </c>
+      <c r="I209" t="str">
+        <f>C209 &amp; " " &amp;L209</f>
+        <v xml:space="preserve">XPERT ULTRA MTB BURDEN XPERT ULTRA</v>
+      </c>
+      <c r="J209" t="s">
+        <v>37</v>
+      </c>
+      <c r="K209"/>
+      <c r="L209" t="s">
+        <v>413</v>
+      </c>
+      <c r="M209"/>
+      <c r="N209">
+        <v>1</v>
+      </c>
+      <c r="O209" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P209">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" s="1">
+        <v>5</v>
+      </c>
+      <c r="C210" t="s">
+        <v>171</v>
+      </c>
+      <c r="D210" t="s">
+        <v>35</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210" t="s">
+        <v>62</v>
+      </c>
+      <c r="H210">
+        <v>113</v>
+      </c>
+      <c r="I210" t="str">
+        <f>C210 &amp; " " &amp;L210</f>
+        <v xml:space="preserve">RIFAMPICIN RESULT XPERT ULTRA</v>
+      </c>
+      <c r="J210" t="s">
+        <v>37</v>
+      </c>
+      <c r="L210" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="N210">
+        <v>1</v>
+      </c>
+      <c r="O210" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P210">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>5</v>
+      </c>
+      <c r="C211" t="s">
+        <v>81</v>
+      </c>
+      <c r="D211" t="s">
+        <v>39</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211"/>
+      <c r="H211">
+        <v>114</v>
+      </c>
+      <c r="I211" t="str">
+        <f>C211 &amp; " " &amp;L211</f>
+        <v xml:space="preserve">TUBERCULOSIS TEST RESULT DATE XPERT ULTRA</v>
+      </c>
+      <c r="J211" t="s">
+        <v>41</v>
+      </c>
+      <c r="K211"/>
+      <c r="L211" t="s">
+        <v>413</v>
+      </c>
+      <c r="M211"/>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P211">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>5</v>
+      </c>
+      <c r="C212" t="s">
+        <v>279</v>
+      </c>
+      <c r="D212" t="s">
+        <v>39</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212"/>
+      <c r="H212">
+        <v>115</v>
+      </c>
+      <c r="I212" t="str">
+        <f>C212 &amp; " " &amp;L212</f>
+        <v xml:space="preserve">DATE OF SENDING TO CULTURE XPERT ULTRA</v>
+      </c>
+      <c r="J212" t="s">
+        <v>41</v>
+      </c>
+      <c r="K212"/>
+      <c r="L212" t="s">
+        <v>413</v>
+      </c>
+      <c r="M212"/>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P212">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>5</v>
+      </c>
+      <c r="C213" t="s">
+        <v>280</v>
+      </c>
+      <c r="D213" t="s">
+        <v>39</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213"/>
+      <c r="H213">
+        <v>116</v>
+      </c>
+      <c r="I213" t="str">
+        <f>C213 &amp; " " &amp;L213</f>
+        <v xml:space="preserve">DATE OF SENDING TO DST XPERT ULTRA</v>
+      </c>
+      <c r="J213" t="s">
+        <v>41</v>
+      </c>
+      <c r="K213"/>
+      <c r="L213" t="s">
+        <v>413</v>
+      </c>
+      <c r="M213"/>
+      <c r="N213">
+        <v>1</v>
+      </c>
+      <c r="O213" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P213">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>5</v>
+      </c>
+      <c r="C214" t="s">
+        <v>282</v>
+      </c>
+      <c r="D214" t="s">
+        <v>35</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214" t="s">
+        <v>295</v>
+      </c>
+      <c r="H214">
+        <v>117</v>
+      </c>
+      <c r="I214" t="str">
+        <f>C214 &amp; " " &amp;L214</f>
+        <v xml:space="preserve">SENT TO CULTURE XPERT ULTRA</v>
+      </c>
+      <c r="J214" t="s">
+        <v>37</v>
+      </c>
+      <c r="K214"/>
+      <c r="L214" t="s">
+        <v>413</v>
+      </c>
+      <c r="M214"/>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P214">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>5</v>
+      </c>
+      <c r="C215" t="s">
+        <v>281</v>
+      </c>
+      <c r="D215" t="s">
+        <v>35</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215" t="s">
+        <v>294</v>
+      </c>
+      <c r="H215">
+        <v>118</v>
+      </c>
+      <c r="I215" t="str">
+        <f>C215 &amp; " " &amp;L215</f>
+        <v xml:space="preserve">SENT TO DST XPERT ULTRA</v>
+      </c>
+      <c r="J215" t="s">
+        <v>37</v>
+      </c>
+      <c r="K215"/>
+      <c r="L215" t="s">
+        <v>413</v>
+      </c>
+      <c r="M215"/>
+      <c r="N215">
+        <v>1</v>
+      </c>
+      <c r="O215" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P215">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>5</v>
+      </c>
+      <c r="C216" t="s">
+        <v>34</v>
+      </c>
+      <c r="D216" t="s">
+        <v>35</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216" t="s">
+        <v>36</v>
+      </c>
+      <c r="H216">
+        <v>119</v>
+      </c>
+      <c r="I216" t="str">
+        <f>C216 &amp; " " &amp;L216</f>
+        <v xml:space="preserve">APPEARANCE OF SPECIMEN XPERT XDR</v>
+      </c>
+      <c r="J216" t="s">
+        <v>37</v>
+      </c>
+      <c r="K216"/>
+      <c r="L216" t="s">
+        <v>426</v>
+      </c>
+      <c r="M216"/>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P216">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>5</v>
+      </c>
+      <c r="C217" t="s">
+        <v>51</v>
+      </c>
+      <c r="D217" t="s">
+        <v>35</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" t="s">
+        <v>52</v>
+      </c>
+      <c r="H217">
+        <v>120</v>
+      </c>
+      <c r="I217" t="str">
+        <f>C217 &amp; " " &amp;L217</f>
+        <v xml:space="preserve">MTB RESULT XPERT XDR</v>
+      </c>
+      <c r="J217" t="s">
+        <v>37</v>
+      </c>
+      <c r="K217"/>
+      <c r="L217" t="s">
+        <v>426</v>
+      </c>
+      <c r="M217"/>
+      <c r="N217">
+        <v>1</v>
+      </c>
+      <c r="O217" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P217">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>5</v>
+      </c>
+      <c r="C218" t="s">
+        <v>85</v>
+      </c>
+      <c r="D218" t="s">
+        <v>44</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218" t="s">
+        <v>45</v>
+      </c>
+      <c r="H218">
+        <v>121</v>
+      </c>
+      <c r="I218" t="str">
+        <f>C218 &amp; " " &amp;L218</f>
+        <v xml:space="preserve">ERROR CODE XPERT XDR</v>
+      </c>
+      <c r="J218" t="s">
+        <v>46</v>
+      </c>
+      <c r="K218"/>
+      <c r="L218" t="s">
+        <v>426</v>
+      </c>
+      <c r="M218"/>
+      <c r="N218">
+        <v>1</v>
+      </c>
+      <c r="O218" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P218">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" s="1">
+        <v>5</v>
+      </c>
+      <c r="C219" t="s">
+        <v>170</v>
+      </c>
+      <c r="D219" t="s">
+        <v>35</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219" t="s">
+        <v>88</v>
+      </c>
+      <c r="H219">
+        <v>122</v>
+      </c>
+      <c r="I219" t="str">
+        <f>C219 &amp; " " &amp;L219</f>
+        <v xml:space="preserve">ISONIAZID RESULT XPERT XDR</v>
+      </c>
+      <c r="J219" t="s">
+        <v>37</v>
+      </c>
+      <c r="L219" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P219">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>5</v>
+      </c>
+      <c r="C220" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D220" t="s">
+        <v>35</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220" t="s">
+        <v>289</v>
+      </c>
+      <c r="H220">
+        <v>123</v>
+      </c>
+      <c r="I220" t="str">
+        <f>C220 &amp; " " &amp;L220</f>
+        <v xml:space="preserve">MOX/OFX RESULT XPERT XDR</v>
+      </c>
+      <c r="J220" t="s">
+        <v>37</v>
+      </c>
+      <c r="L220" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P220">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>5</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="D221" t="s">
+        <v>35</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221" t="s">
+        <v>288</v>
+      </c>
+      <c r="H221">
+        <v>124</v>
+      </c>
+      <c r="I221" t="str">
+        <f>C221 &amp; " " &amp;L221</f>
+        <v xml:space="preserve">KM/AM/CM RESULT XPERT XDR</v>
+      </c>
+      <c r="J221" t="s">
+        <v>37</v>
+      </c>
+      <c r="L221" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N221">
+        <v>1</v>
+      </c>
+      <c r="O221" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P221">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" s="1">
+        <v>5</v>
+      </c>
+      <c r="C222" t="s">
+        <v>434</v>
+      </c>
+      <c r="D222" t="s">
+        <v>35</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222" t="s">
+        <v>435</v>
+      </c>
+      <c r="H222">
+        <v>125</v>
+      </c>
+      <c r="I222" t="str">
+        <f>C222 &amp; " " &amp;L222</f>
+        <v xml:space="preserve">ETHIONAMIDE RESULT XPERT XDR</v>
+      </c>
+      <c r="J222" t="s">
+        <v>37</v>
+      </c>
+      <c r="L222" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P222">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>5</v>
+      </c>
+      <c r="C223" t="s">
+        <v>81</v>
+      </c>
+      <c r="D223" t="s">
+        <v>39</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223"/>
+      <c r="H223">
+        <v>126</v>
+      </c>
+      <c r="I223" t="str">
+        <f>C223 &amp; " " &amp;L223</f>
+        <v xml:space="preserve">TUBERCULOSIS TEST RESULT DATE XPERT XDR</v>
+      </c>
+      <c r="J223" t="s">
+        <v>41</v>
+      </c>
+      <c r="K223"/>
+      <c r="L223" t="s">
+        <v>426</v>
+      </c>
+      <c r="M223"/>
+      <c r="N223">
+        <v>1</v>
+      </c>
+      <c r="O223" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P223">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>5</v>
+      </c>
+      <c r="C224" t="s">
+        <v>279</v>
+      </c>
+      <c r="D224" t="s">
+        <v>39</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>1</v>
+      </c>
+      <c r="G224"/>
+      <c r="H224">
+        <v>127</v>
+      </c>
+      <c r="I224" t="str">
+        <f>C224 &amp; " " &amp;L224</f>
+        <v xml:space="preserve">DATE OF SENDING TO CULTURE XPERT XDR</v>
+      </c>
+      <c r="J224" t="s">
+        <v>41</v>
+      </c>
+      <c r="K224"/>
+      <c r="L224" t="s">
+        <v>426</v>
+      </c>
+      <c r="M224"/>
+      <c r="N224">
+        <v>1</v>
+      </c>
+      <c r="O224" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P224">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>5</v>
+      </c>
+      <c r="C225" t="s">
+        <v>280</v>
+      </c>
+      <c r="D225" t="s">
+        <v>39</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225"/>
+      <c r="H225">
+        <v>128</v>
+      </c>
+      <c r="I225" t="str">
+        <f>C225 &amp; " " &amp;L225</f>
+        <v xml:space="preserve">DATE OF SENDING TO DST XPERT XDR</v>
+      </c>
+      <c r="J225" t="s">
+        <v>41</v>
+      </c>
+      <c r="K225"/>
+      <c r="L225" t="s">
+        <v>426</v>
+      </c>
+      <c r="M225"/>
+      <c r="N225">
+        <v>1</v>
+      </c>
+      <c r="O225" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P225">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>5</v>
+      </c>
+      <c r="C226" t="s">
+        <v>282</v>
+      </c>
+      <c r="D226" t="s">
+        <v>35</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>1</v>
+      </c>
+      <c r="G226" t="s">
+        <v>295</v>
+      </c>
+      <c r="H226">
+        <v>129</v>
+      </c>
+      <c r="I226" t="str">
+        <f>C226 &amp; " " &amp;L226</f>
+        <v xml:space="preserve">SENT TO CULTURE XPERT XDR</v>
+      </c>
+      <c r="J226" t="s">
+        <v>37</v>
+      </c>
+      <c r="K226"/>
+      <c r="L226" t="s">
+        <v>426</v>
+      </c>
+      <c r="M226"/>
+      <c r="N226">
+        <v>1</v>
+      </c>
+      <c r="O226" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P226">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>5</v>
+      </c>
+      <c r="C227" t="s">
+        <v>281</v>
+      </c>
+      <c r="D227" t="s">
+        <v>35</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227" t="s">
+        <v>294</v>
+      </c>
+      <c r="H227">
+        <v>130</v>
+      </c>
+      <c r="I227" t="str">
+        <f>C227 &amp; " " &amp;L227</f>
+        <v xml:space="preserve">SENT TO DST XPERT XDR</v>
+      </c>
+      <c r="J227" t="s">
+        <v>37</v>
+      </c>
+      <c r="K227"/>
+      <c r="L227" t="s">
+        <v>426</v>
+      </c>
+      <c r="M227"/>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227" s="4">
+        <v>46313</v>
+      </c>
+      <c r="P227">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>441</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q205" xr:uid="{91536433-8730-4EA0-BCCE-0E80DA08A6A5}"/>
-  <conditionalFormatting sqref="Q2:Q205">
+  <autoFilter ref="A1:Q227" xr:uid="{91536433-8730-4EA0-BCCE-0E80DA08A6A5}"/>
+  <conditionalFormatting sqref="Q2:Q227">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/commonlab.xlsx
+++ b/resources/commonlab.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="474">
   <si>
     <t>uuid</t>
   </si>
@@ -1375,6 +1375,102 @@
   </si>
   <si>
     <t>f399e490-ed5a-474f-a755-63d22092e05f</t>
+  </si>
+  <si>
+    <t>3bb32248-55b5-4513-a681-2f753646a543</t>
+  </si>
+  <si>
+    <t>XPERT ULTRA RESULT</t>
+  </si>
+  <si>
+    <t>0075b266-74f3-4ed7-a822-369ffe92c7b2</t>
+  </si>
+  <si>
+    <t>TEST NUMBER</t>
+  </si>
+  <si>
+    <t>Regex=[0-9A-Za-z/-]*</t>
+  </si>
+  <si>
+    <t>0d35f6db-f13a-4c4a-9a9a-0fc14d2167d2</t>
+  </si>
+  <si>
+    <t>LAB</t>
+  </si>
+  <si>
+    <t>17b6e353-8488-4fb2-b100-6574b41d15be</t>
+  </si>
+  <si>
+    <t>736346b3-54c5-491e-95db-0c76b65630c3</t>
+  </si>
+  <si>
+    <t>fc66e7d3-632b-4fda-9eb6-b64844228412</t>
+  </si>
+  <si>
+    <t>XPERT XDR RESULT</t>
+  </si>
+  <si>
+    <t>9e2b0d1b-9bb3-4761-bf84-0668bed74e92</t>
+  </si>
+  <si>
+    <t>ISONIAZID (H)</t>
+  </si>
+  <si>
+    <t>e03067c3-2e0d-4b27-aaa7-0a21683e2543</t>
+  </si>
+  <si>
+    <t>9ed60f80-acf9-4ef8-930e-f02be2a7aeb5</t>
+  </si>
+  <si>
+    <t>FLUOROQUINOLONES (FQ)</t>
+  </si>
+  <si>
+    <t>32342299-8bc1-4eb2-a02e-797140ee763e</t>
+  </si>
+  <si>
+    <t>42630a36-b380-4fcd-9ef3-12e2efb8fad3</t>
+  </si>
+  <si>
+    <t>AMIKACIN (AM)</t>
+  </si>
+  <si>
+    <t>ab9ebf0d-767b-4319-abdb-86bede788c20</t>
+  </si>
+  <si>
+    <t>c202c6e1-0057-4ff2-84cb-8d53d86e5fc2</t>
+  </si>
+  <si>
+    <t>CAPREOMYCIN (CM)</t>
+  </si>
+  <si>
+    <t>84156f85-6d51-43ae-8dfd-90563027b9b8</t>
+  </si>
+  <si>
+    <t>34b96045-b2c1-4165-9390-3dd12153e1f5</t>
+  </si>
+  <si>
+    <t>KANAMYCIN (KM)</t>
+  </si>
+  <si>
+    <t>bdf9767b-745e-4d67-9c91-786030507a16</t>
+  </si>
+  <si>
+    <t>8a2f3e93-aa83-44f9-abc3-a4a5eeadb8c9</t>
+  </si>
+  <si>
+    <t>PROTHIONAMIDE/ETHIONAMIDE (PTO/ETO)</t>
+  </si>
+  <si>
+    <t>a3820030-1c76-4251-8323-7f33f7f56761</t>
+  </si>
+  <si>
+    <t>74c78a90-ea77-43d6-a77e-ca4a55de65a7</t>
+  </si>
+  <si>
+    <t>c13bd24b-f54d-4d08-bcf5-9e1c4d60c3fb</t>
+  </si>
+  <si>
+    <t>ae1c0f6e-bf21-423c-a286-0e9cbf3e0a01</t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91536433-8730-4EA0-BCCE-0E80DA08A6A5}">
-  <dimension ref="A1:Q227"/>
+  <dimension ref="A1:Q219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -11659,10 +11755,10 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="D206" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -11670,18 +11766,16 @@
       <c r="F206">
         <v>1</v>
       </c>
-      <c r="G206" t="s">
-        <v>36</v>
-      </c>
+      <c r="G206"/>
       <c r="H206">
         <v>109</v>
       </c>
       <c r="I206" t="str">
         <f>C206 &amp; " " &amp;L206</f>
-        <v xml:space="preserve">APPEARANCE OF SPECIMEN XPERT ULTRA</v>
+        <v xml:space="preserve">TUBERCULOSIS TEST RESULT DATE XPERT ULTRA</v>
       </c>
       <c r="J206" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K206"/>
       <c r="L206" t="s">
@@ -11692,13 +11786,13 @@
         <v>1</v>
       </c>
       <c r="O206" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P206">
         <v>0</v>
       </c>
       <c r="Q206" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
     </row>
     <row r="207" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -11709,7 +11803,7 @@
         <v>5</v>
       </c>
       <c r="C207" t="s">
-        <v>51</v>
+        <v>443</v>
       </c>
       <c r="D207" t="s">
         <v>35</v>
@@ -11721,14 +11815,14 @@
         <v>1</v>
       </c>
       <c r="G207" t="s">
-        <v>52</v>
+        <v>418</v>
       </c>
       <c r="H207">
         <v>110</v>
       </c>
       <c r="I207" t="str">
         <f>C207 &amp; " " &amp;L207</f>
-        <v xml:space="preserve">MTB RESULT XPERT ULTRA</v>
+        <v xml:space="preserve">XPERT ULTRA RESULT XPERT ULTRA</v>
       </c>
       <c r="J207" t="s">
         <v>37</v>
@@ -11742,13 +11836,13 @@
         <v>1</v>
       </c>
       <c r="O207" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P207">
         <v>0</v>
       </c>
       <c r="Q207" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
     </row>
     <row r="208" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -11759,10 +11853,10 @@
         <v>5</v>
       </c>
       <c r="C208" t="s">
-        <v>85</v>
+        <v>445</v>
       </c>
       <c r="D208" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -11771,17 +11865,17 @@
         <v>1</v>
       </c>
       <c r="G208" t="s">
-        <v>45</v>
+        <v>446</v>
       </c>
       <c r="H208">
         <v>111</v>
       </c>
       <c r="I208" t="str">
         <f>C208 &amp; " " &amp;L208</f>
-        <v xml:space="preserve">ERROR CODE XPERT ULTRA</v>
+        <v xml:space="preserve">TEST NUMBER XPERT ULTRA</v>
       </c>
       <c r="J208" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K208"/>
       <c r="L208" t="s">
@@ -11792,13 +11886,13 @@
         <v>1</v>
       </c>
       <c r="O208" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P208">
         <v>0</v>
       </c>
       <c r="Q208" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -11809,7 +11903,7 @@
         <v>5</v>
       </c>
       <c r="C209" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="D209" t="s">
         <v>35</v>
@@ -11821,14 +11915,14 @@
         <v>1</v>
       </c>
       <c r="G209" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="H209">
         <v>112</v>
       </c>
       <c r="I209" t="str">
         <f>C209 &amp; " " &amp;L209</f>
-        <v xml:space="preserve">XPERT ULTRA MTB BURDEN XPERT ULTRA</v>
+        <v xml:space="preserve">LAB XPERT ULTRA</v>
       </c>
       <c r="J209" t="s">
         <v>37</v>
@@ -11842,27 +11936,27 @@
         <v>1</v>
       </c>
       <c r="O209" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P209">
         <v>0</v>
       </c>
       <c r="Q209" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
-      <c r="B210" s="1">
+      <c r="B210">
         <v>5</v>
       </c>
       <c r="C210" t="s">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="D210" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -11870,33 +11964,33 @@
       <c r="F210">
         <v>1</v>
       </c>
-      <c r="G210" t="s">
-        <v>62</v>
-      </c>
+      <c r="G210"/>
       <c r="H210">
         <v>113</v>
       </c>
       <c r="I210" t="str">
         <f>C210 &amp; " " &amp;L210</f>
-        <v xml:space="preserve">RIFAMPICIN RESULT XPERT ULTRA</v>
+        <v xml:space="preserve">TUBERCULOSIS TEST RESULT DATE XPERT XDR</v>
       </c>
       <c r="J210" t="s">
-        <v>37</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>413</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K210"/>
+      <c r="L210" t="s">
+        <v>426</v>
+      </c>
+      <c r="M210"/>
       <c r="N210">
         <v>1</v>
       </c>
       <c r="O210" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P210">
         <v>0</v>
       </c>
       <c r="Q210" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -11907,10 +12001,10 @@
         <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>81</v>
+        <v>452</v>
       </c>
       <c r="D211" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -11918,33 +12012,35 @@
       <c r="F211">
         <v>1</v>
       </c>
-      <c r="G211"/>
+      <c r="G211" t="s">
+        <v>435</v>
+      </c>
       <c r="H211">
         <v>114</v>
       </c>
       <c r="I211" t="str">
         <f>C211 &amp; " " &amp;L211</f>
-        <v xml:space="preserve">TUBERCULOSIS TEST RESULT DATE XPERT ULTRA</v>
+        <v xml:space="preserve">XPERT XDR RESULT XPERT XDR</v>
       </c>
       <c r="J211" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K211"/>
       <c r="L211" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="M211"/>
       <c r="N211">
         <v>1</v>
       </c>
       <c r="O211" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P211">
         <v>0</v>
       </c>
       <c r="Q211" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -11955,10 +12051,10 @@
         <v>5</v>
       </c>
       <c r="C212" t="s">
-        <v>279</v>
+        <v>454</v>
       </c>
       <c r="D212" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -11966,33 +12062,35 @@
       <c r="F212">
         <v>1</v>
       </c>
-      <c r="G212"/>
+      <c r="G212" t="s">
+        <v>455</v>
+      </c>
       <c r="H212">
         <v>115</v>
       </c>
       <c r="I212" t="str">
         <f>C212 &amp; " " &amp;L212</f>
-        <v xml:space="preserve">DATE OF SENDING TO CULTURE XPERT ULTRA</v>
+        <v xml:space="preserve">ISONIAZID (H) XPERT XDR</v>
       </c>
       <c r="J212" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K212"/>
       <c r="L212" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="M212"/>
       <c r="N212">
         <v>1</v>
       </c>
       <c r="O212" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P212">
         <v>0</v>
       </c>
       <c r="Q212" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12003,10 +12101,10 @@
         <v>5</v>
       </c>
       <c r="C213" t="s">
-        <v>280</v>
+        <v>457</v>
       </c>
       <c r="D213" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -12014,33 +12112,35 @@
       <c r="F213">
         <v>1</v>
       </c>
-      <c r="G213"/>
+      <c r="G213" t="s">
+        <v>458</v>
+      </c>
       <c r="H213">
         <v>116</v>
       </c>
       <c r="I213" t="str">
         <f>C213 &amp; " " &amp;L213</f>
-        <v xml:space="preserve">DATE OF SENDING TO DST XPERT ULTRA</v>
+        <v xml:space="preserve">FLUOROQUINOLONES (FQ) XPERT XDR</v>
       </c>
       <c r="J213" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K213"/>
       <c r="L213" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="M213"/>
       <c r="N213">
         <v>1</v>
       </c>
       <c r="O213" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P213">
         <v>0</v>
       </c>
       <c r="Q213" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12051,7 +12151,7 @@
         <v>5</v>
       </c>
       <c r="C214" t="s">
-        <v>282</v>
+        <v>460</v>
       </c>
       <c r="D214" t="s">
         <v>35</v>
@@ -12063,34 +12163,34 @@
         <v>1</v>
       </c>
       <c r="G214" t="s">
-        <v>295</v>
+        <v>461</v>
       </c>
       <c r="H214">
         <v>117</v>
       </c>
       <c r="I214" t="str">
         <f>C214 &amp; " " &amp;L214</f>
-        <v xml:space="preserve">SENT TO CULTURE XPERT ULTRA</v>
+        <v xml:space="preserve">AMIKACIN (AM) XPERT XDR</v>
       </c>
       <c r="J214" t="s">
         <v>37</v>
       </c>
       <c r="K214"/>
       <c r="L214" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="M214"/>
       <c r="N214">
         <v>1</v>
       </c>
       <c r="O214" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P214">
         <v>0</v>
       </c>
       <c r="Q214" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
     </row>
     <row r="215" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12101,7 +12201,7 @@
         <v>5</v>
       </c>
       <c r="C215" t="s">
-        <v>281</v>
+        <v>463</v>
       </c>
       <c r="D215" t="s">
         <v>35</v>
@@ -12113,34 +12213,34 @@
         <v>1</v>
       </c>
       <c r="G215" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="H215">
         <v>118</v>
       </c>
       <c r="I215" t="str">
         <f>C215 &amp; " " &amp;L215</f>
-        <v xml:space="preserve">SENT TO DST XPERT ULTRA</v>
+        <v xml:space="preserve">CAPREOMYCIN (CM) XPERT XDR</v>
       </c>
       <c r="J215" t="s">
         <v>37</v>
       </c>
       <c r="K215"/>
       <c r="L215" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="M215"/>
       <c r="N215">
         <v>1</v>
       </c>
       <c r="O215" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P215">
         <v>0</v>
       </c>
       <c r="Q215" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12151,7 +12251,7 @@
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>34</v>
+        <v>466</v>
       </c>
       <c r="D216" t="s">
         <v>35</v>
@@ -12163,14 +12263,14 @@
         <v>1</v>
       </c>
       <c r="G216" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="H216">
         <v>119</v>
       </c>
       <c r="I216" t="str">
         <f>C216 &amp; " " &amp;L216</f>
-        <v xml:space="preserve">APPEARANCE OF SPECIMEN XPERT XDR</v>
+        <v xml:space="preserve">KANAMYCIN (KM) XPERT XDR</v>
       </c>
       <c r="J216" t="s">
         <v>37</v>
@@ -12184,13 +12284,13 @@
         <v>1</v>
       </c>
       <c r="O216" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P216">
         <v>0</v>
       </c>
       <c r="Q216" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
     </row>
     <row r="217" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12201,7 +12301,7 @@
         <v>5</v>
       </c>
       <c r="C217" t="s">
-        <v>51</v>
+        <v>469</v>
       </c>
       <c r="D217" t="s">
         <v>35</v>
@@ -12213,14 +12313,14 @@
         <v>1</v>
       </c>
       <c r="G217" t="s">
-        <v>52</v>
+        <v>470</v>
       </c>
       <c r="H217">
         <v>120</v>
       </c>
       <c r="I217" t="str">
         <f>C217 &amp; " " &amp;L217</f>
-        <v xml:space="preserve">MTB RESULT XPERT XDR</v>
+        <v xml:space="preserve">PROTHIONAMIDE/ETHIONAMIDE (PTO/ETO) XPERT XDR</v>
       </c>
       <c r="J217" t="s">
         <v>37</v>
@@ -12234,13 +12334,13 @@
         <v>1</v>
       </c>
       <c r="O217" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P217">
         <v>0</v>
       </c>
       <c r="Q217" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
     </row>
     <row r="218" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12251,10 +12351,10 @@
         <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>85</v>
+        <v>445</v>
       </c>
       <c r="D218" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -12263,17 +12363,17 @@
         <v>1</v>
       </c>
       <c r="G218" t="s">
-        <v>45</v>
+        <v>446</v>
       </c>
       <c r="H218">
         <v>121</v>
       </c>
       <c r="I218" t="str">
         <f>C218 &amp; " " &amp;L218</f>
-        <v xml:space="preserve">ERROR CODE XPERT XDR</v>
+        <v xml:space="preserve">TEST NUMBER XPERT XDR</v>
       </c>
       <c r="J218" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K218"/>
       <c r="L218" t="s">
@@ -12284,24 +12384,24 @@
         <v>1</v>
       </c>
       <c r="O218" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P218">
         <v>0</v>
       </c>
       <c r="Q218" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" s="1">
+      <c r="B219">
         <v>5</v>
       </c>
       <c r="C219" t="s">
-        <v>170</v>
+        <v>448</v>
       </c>
       <c r="D219" t="s">
         <v>35</v>
@@ -12313,425 +12413,39 @@
         <v>1</v>
       </c>
       <c r="G219" t="s">
-        <v>88</v>
+        <v>449</v>
       </c>
       <c r="H219">
         <v>122</v>
       </c>
       <c r="I219" t="str">
         <f>C219 &amp; " " &amp;L219</f>
-        <v xml:space="preserve">ISONIAZID RESULT XPERT XDR</v>
+        <v xml:space="preserve">LAB XPERT XDR</v>
       </c>
       <c r="J219" t="s">
         <v>37</v>
       </c>
-      <c r="L219" s="1" t="s">
+      <c r="K219"/>
+      <c r="L219" t="s">
         <v>426</v>
       </c>
+      <c r="M219"/>
       <c r="N219">
         <v>1</v>
       </c>
       <c r="O219" s="4">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="P219">
         <v>0</v>
       </c>
       <c r="Q219" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A220">
-        <v>219</v>
-      </c>
-      <c r="B220">
-        <v>5</v>
-      </c>
-      <c r="C220" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="D220" t="s">
-        <v>35</v>
-      </c>
-      <c r="E220">
-        <v>0</v>
-      </c>
-      <c r="F220">
-        <v>1</v>
-      </c>
-      <c r="G220" t="s">
-        <v>289</v>
-      </c>
-      <c r="H220">
-        <v>123</v>
-      </c>
-      <c r="I220" t="str">
-        <f>C220 &amp; " " &amp;L220</f>
-        <v xml:space="preserve">MOX/OFX RESULT XPERT XDR</v>
-      </c>
-      <c r="J220" t="s">
-        <v>37</v>
-      </c>
-      <c r="L220" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="N220">
-        <v>1</v>
-      </c>
-      <c r="O220" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P220">
-        <v>0</v>
-      </c>
-      <c r="Q220" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A221">
-        <v>220</v>
-      </c>
-      <c r="B221">
-        <v>5</v>
-      </c>
-      <c r="C221" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="D221" t="s">
-        <v>35</v>
-      </c>
-      <c r="E221">
-        <v>0</v>
-      </c>
-      <c r="F221">
-        <v>1</v>
-      </c>
-      <c r="G221" t="s">
-        <v>288</v>
-      </c>
-      <c r="H221">
-        <v>124</v>
-      </c>
-      <c r="I221" t="str">
-        <f>C221 &amp; " " &amp;L221</f>
-        <v xml:space="preserve">KM/AM/CM RESULT XPERT XDR</v>
-      </c>
-      <c r="J221" t="s">
-        <v>37</v>
-      </c>
-      <c r="L221" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="N221">
-        <v>1</v>
-      </c>
-      <c r="O221" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P221">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A222">
-        <v>221</v>
-      </c>
-      <c r="B222" s="1">
-        <v>5</v>
-      </c>
-      <c r="C222" t="s">
-        <v>434</v>
-      </c>
-      <c r="D222" t="s">
-        <v>35</v>
-      </c>
-      <c r="E222">
-        <v>0</v>
-      </c>
-      <c r="F222">
-        <v>1</v>
-      </c>
-      <c r="G222" t="s">
-        <v>435</v>
-      </c>
-      <c r="H222">
-        <v>125</v>
-      </c>
-      <c r="I222" t="str">
-        <f>C222 &amp; " " &amp;L222</f>
-        <v xml:space="preserve">ETHIONAMIDE RESULT XPERT XDR</v>
-      </c>
-      <c r="J222" t="s">
-        <v>37</v>
-      </c>
-      <c r="L222" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="N222">
-        <v>1</v>
-      </c>
-      <c r="O222" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P222">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A223">
-        <v>222</v>
-      </c>
-      <c r="B223">
-        <v>5</v>
-      </c>
-      <c r="C223" t="s">
-        <v>81</v>
-      </c>
-      <c r="D223" t="s">
-        <v>39</v>
-      </c>
-      <c r="E223">
-        <v>0</v>
-      </c>
-      <c r="F223">
-        <v>1</v>
-      </c>
-      <c r="G223"/>
-      <c r="H223">
-        <v>126</v>
-      </c>
-      <c r="I223" t="str">
-        <f>C223 &amp; " " &amp;L223</f>
-        <v xml:space="preserve">TUBERCULOSIS TEST RESULT DATE XPERT XDR</v>
-      </c>
-      <c r="J223" t="s">
-        <v>41</v>
-      </c>
-      <c r="K223"/>
-      <c r="L223" t="s">
-        <v>426</v>
-      </c>
-      <c r="M223"/>
-      <c r="N223">
-        <v>1</v>
-      </c>
-      <c r="O223" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P223">
-        <v>0</v>
-      </c>
-      <c r="Q223" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A224">
-        <v>223</v>
-      </c>
-      <c r="B224">
-        <v>5</v>
-      </c>
-      <c r="C224" t="s">
-        <v>279</v>
-      </c>
-      <c r="D224" t="s">
-        <v>39</v>
-      </c>
-      <c r="E224">
-        <v>0</v>
-      </c>
-      <c r="F224">
-        <v>1</v>
-      </c>
-      <c r="G224"/>
-      <c r="H224">
-        <v>127</v>
-      </c>
-      <c r="I224" t="str">
-        <f>C224 &amp; " " &amp;L224</f>
-        <v xml:space="preserve">DATE OF SENDING TO CULTURE XPERT XDR</v>
-      </c>
-      <c r="J224" t="s">
-        <v>41</v>
-      </c>
-      <c r="K224"/>
-      <c r="L224" t="s">
-        <v>426</v>
-      </c>
-      <c r="M224"/>
-      <c r="N224">
-        <v>1</v>
-      </c>
-      <c r="O224" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P224">
-        <v>0</v>
-      </c>
-      <c r="Q224" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A225">
-        <v>224</v>
-      </c>
-      <c r="B225">
-        <v>5</v>
-      </c>
-      <c r="C225" t="s">
-        <v>280</v>
-      </c>
-      <c r="D225" t="s">
-        <v>39</v>
-      </c>
-      <c r="E225">
-        <v>0</v>
-      </c>
-      <c r="F225">
-        <v>1</v>
-      </c>
-      <c r="G225"/>
-      <c r="H225">
-        <v>128</v>
-      </c>
-      <c r="I225" t="str">
-        <f>C225 &amp; " " &amp;L225</f>
-        <v xml:space="preserve">DATE OF SENDING TO DST XPERT XDR</v>
-      </c>
-      <c r="J225" t="s">
-        <v>41</v>
-      </c>
-      <c r="K225"/>
-      <c r="L225" t="s">
-        <v>426</v>
-      </c>
-      <c r="M225"/>
-      <c r="N225">
-        <v>1</v>
-      </c>
-      <c r="O225" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P225">
-        <v>0</v>
-      </c>
-      <c r="Q225" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="226" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A226">
-        <v>225</v>
-      </c>
-      <c r="B226">
-        <v>5</v>
-      </c>
-      <c r="C226" t="s">
-        <v>282</v>
-      </c>
-      <c r="D226" t="s">
-        <v>35</v>
-      </c>
-      <c r="E226">
-        <v>0</v>
-      </c>
-      <c r="F226">
-        <v>1</v>
-      </c>
-      <c r="G226" t="s">
-        <v>295</v>
-      </c>
-      <c r="H226">
-        <v>129</v>
-      </c>
-      <c r="I226" t="str">
-        <f>C226 &amp; " " &amp;L226</f>
-        <v xml:space="preserve">SENT TO CULTURE XPERT XDR</v>
-      </c>
-      <c r="J226" t="s">
-        <v>37</v>
-      </c>
-      <c r="K226"/>
-      <c r="L226" t="s">
-        <v>426</v>
-      </c>
-      <c r="M226"/>
-      <c r="N226">
-        <v>1</v>
-      </c>
-      <c r="O226" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P226">
-        <v>0</v>
-      </c>
-      <c r="Q226" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="227" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A227">
-        <v>226</v>
-      </c>
-      <c r="B227">
-        <v>5</v>
-      </c>
-      <c r="C227" t="s">
-        <v>281</v>
-      </c>
-      <c r="D227" t="s">
-        <v>35</v>
-      </c>
-      <c r="E227">
-        <v>0</v>
-      </c>
-      <c r="F227">
-        <v>1</v>
-      </c>
-      <c r="G227" t="s">
-        <v>294</v>
-      </c>
-      <c r="H227">
-        <v>130</v>
-      </c>
-      <c r="I227" t="str">
-        <f>C227 &amp; " " &amp;L227</f>
-        <v xml:space="preserve">SENT TO DST XPERT XDR</v>
-      </c>
-      <c r="J227" t="s">
-        <v>37</v>
-      </c>
-      <c r="K227"/>
-      <c r="L227" t="s">
-        <v>426</v>
-      </c>
-      <c r="M227"/>
-      <c r="N227">
-        <v>1</v>
-      </c>
-      <c r="O227" s="4">
-        <v>46313</v>
-      </c>
-      <c r="P227">
-        <v>0</v>
-      </c>
-      <c r="Q227" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q227" xr:uid="{91536433-8730-4EA0-BCCE-0E80DA08A6A5}"/>
-  <conditionalFormatting sqref="Q2:Q227">
+  <autoFilter ref="A1:Q219" xr:uid="{91536433-8730-4EA0-BCCE-0E80DA08A6A5}"/>
+  <conditionalFormatting sqref="Q2:Q219">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
